--- a/青甘大环线7天行程及详细预算.xlsx
+++ b/青甘大环线7天行程及详细预算.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R86c553e537514b0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6dea99e9bad84c50"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1315,7 +1315,7 @@
         <x:v>D1</x:v>
       </x:c>
       <x:c r="B2" s="33" t="n">
-        <x:v>46244</x:v>
+        <x:v>46243</x:v>
       </x:c>
       <x:c r="C2" s="32" t="str">
         <x:v>抵达西宁</x:v>
@@ -1360,7 +1360,7 @@
         <x:v>D2</x:v>
       </x:c>
       <x:c r="B3" s="33" t="n">
-        <x:v>46245</x:v>
+        <x:v>46244</x:v>
       </x:c>
       <x:c r="C3" s="32" t="str">
         <x:v>西宁</x:v>
@@ -1407,7 +1407,7 @@
         <x:v>D3</x:v>
       </x:c>
       <x:c r="B4" s="33" t="n">
-        <x:v>46246</x:v>
+        <x:v>46245</x:v>
       </x:c>
       <x:c r="C4" s="32" t="str">
         <x:v>祁连县</x:v>
@@ -1458,7 +1458,7 @@
         <x:v>D4</x:v>
       </x:c>
       <x:c r="B5" s="33" t="n">
-        <x:v>46247</x:v>
+        <x:v>46246</x:v>
       </x:c>
       <x:c r="C5" s="32" t="str">
         <x:v>茶卡</x:v>
@@ -1505,7 +1505,7 @@
         <x:v>D5</x:v>
       </x:c>
       <x:c r="B6" s="33" t="n">
-        <x:v>46248</x:v>
+        <x:v>46247</x:v>
       </x:c>
       <x:c r="C6" s="32" t="str">
         <x:v>大柴旦</x:v>
@@ -1552,7 +1552,7 @@
         <x:v>D6</x:v>
       </x:c>
       <x:c r="B7" s="33" t="n">
-        <x:v>46249</x:v>
+        <x:v>46248</x:v>
       </x:c>
       <x:c r="C7" s="32" t="str">
         <x:v>水上雅丹</x:v>
@@ -1603,7 +1603,7 @@
         <x:v>D7</x:v>
       </x:c>
       <x:c r="B8" s="33" t="n">
-        <x:v>46250</x:v>
+        <x:v>46249</x:v>
       </x:c>
       <x:c r="C8" s="32" t="str">
         <x:v>敦煌</x:v>
@@ -1620,7 +1620,7 @@
       </x:c>
       <x:c r="G8" s="35" t="str">
         <x:v>续住前一晚敦煌酒店
-  按 8/16–8/17 一晚计算，实际以续住页面为准</x:v>
+  按 8/15–8/16 一晚计算，实际以续住页面为准</x:v>
       </x:c>
       <x:c r="H8" s="32" t="str">
         <x:v>¥212–581</x:v>
@@ -1640,7 +1640,7 @@
         <x:v>合计</x:v>
       </x:c>
       <x:c r="B9" s="38" t="str">
-        <x:v>8/10–8/16</x:v>
+        <x:v>8/9–8/15</x:v>
       </x:c>
       <x:c r="C9" s="38" t="str">
         <x:v>西宁</x:v>
@@ -1691,7 +1691,7 @@
     </x:row>
     <x:row r="11" s="1" customFormat="1" ht="124" customHeight="1">
       <x:c r="A11" s="41" t="str">
-        <x:v>预订与安全提醒：8 月 10 日为到达日；8 月 11–16 日每天 09:00 出发。 提前确认西宁取车、敦煌异地还车；如租车公司不支持，可改为包车。 莫高窟按实名预约场次安排，预约时间会影响 D7 的具体顺序。 荒漠路段见站加油，提前下载离线地图；G315 不在行车道内停车拍照。 酒店价格查询于 2026 年 7 月 23 日，按 1 间 2 人、对应日期 1 晚整理；预算按 8 人、4 间、7 晚计算，价格和房态以预订页最终结算为准。</x:v>
+        <x:v>预订与安全提醒：8 月 9 日为到达日；8 月 10–15 日每天 09:00 出发。 提前确认西宁取车、敦煌异地还车；如租车公司不支持，可改为包车。 莫高窟按实名预约场次安排，预约时间会影响 D7 的具体顺序。 荒漠路段见站加油，提前下载离线地图；G315 不在行车道内停车拍照。 酒店价格于 2026 年 7 月 23 日查询，现作为 8 月旺季参考；入住日已调整，价格和房态需在预订页重新确认。预算按 8 人、4 间、7 晚计算。</x:v>
       </x:c>
       <x:c r="B11" s="41"/>
       <x:c r="C11" s="41"/>
@@ -2012,7 +2012,7 @@
         <x:v>166</x:v>
       </x:c>
       <x:c r="I21" s="34" t="str">
-        <x:v>Trip.com 2026-08-10 含税公开价</x:v>
+        <x:v>Trip.com 2026-07-23 查询的同酒店旺季含税参考价；入住日需重新确认</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="58" customHeight="1">
@@ -2068,7 +2068,7 @@
         <x:v>259</x:v>
       </x:c>
       <x:c r="I23" s="48" t="str">
-        <x:v>Trip.com 2026-08-12 含税公开价</x:v>
+        <x:v>Trip.com 2026-07-23 查询的同酒店旺季含税参考价；入住日需重新确认</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="58" customHeight="1">
@@ -2152,7 +2152,7 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="I26" s="48" t="str">
-        <x:v>Trip.com 2026-08-15 含税公开价</x:v>
+        <x:v>Trip.com 2026-07-23 查询的同酒店旺季含税参考价；入住日需重新确认</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="58" customHeight="1">

--- a/青甘大环线7天行程及详细预算.xlsx
+++ b/青甘大环线7天行程及详细预算.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6dea99e9bad84c50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4400d0e2310048f7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -658,7 +658,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="61">
+  <x:cellXfs count="54">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -800,47 +800,26 @@
     <x:xf numFmtId="0" fontId="19" fillId="40" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="28" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="28" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="201" fontId="28" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="201" fontId="28" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="202" fontId="28" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="28" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="202" fontId="29" fillId="38" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="203" fontId="28" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="28" fillId="37" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="202" fontId="28" fillId="37" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="29" fillId="37" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="202" fontId="29" fillId="37" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="28" fillId="39" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="28" fillId="39" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="49">
@@ -1263,7 +1242,7 @@
     <x:col min="1" max="1" width="8" style="1" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="9" style="1" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="13" style="1" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="48" style="1" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="58" style="1" hidden="0" customWidth="1"/>
     <x:col min="5" max="6" width="17.778846740722656" style="1" customWidth="1"/>
     <x:col min="7" max="7" width="48" style="1" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="19" style="1" hidden="0" customWidth="1"/>
@@ -1286,7 +1265,7 @@
         <x:v>出发城市</x:v>
       </x:c>
       <x:c r="D1" s="31" t="str">
-        <x:v>行程安排</x:v>
+        <x:v>日间行程（时间轴）</x:v>
       </x:c>
       <x:c r="E1" s="31" t="str">
         <x:v>抵达城市</x:v>
@@ -1310,7 +1289,7 @@
       <x:c r="N1" s="21"/>
       <x:c r="O1" s="21"/>
     </x:row>
-    <x:row r="2" s="1" customFormat="1" ht="122" customHeight="1">
+    <x:row r="2" s="1" customFormat="1" ht="174" customHeight="1">
       <x:c r="A2" s="32" t="str">
         <x:v>D1</x:v>
       </x:c>
@@ -1321,9 +1300,12 @@
         <x:v>抵达西宁</x:v>
       </x:c>
       <x:c r="D2" s="34" t="str">
-        <x:v>按航班或车次抵达西宁，前往酒店办理入住
-下午以休息、取车和补充随车物资为主
-时间充裕可在市区散步或就近用餐，为次日环线留足体力</x:v>
+        <x:v>抵达时｜西宁机场 / 火车站
+↓ 约 30–60 min 市内接驳
+抵达后｜酒店办理入住｜西宁海拔约 2,260 m
+午餐｜按实际抵达时间在机场、车站或酒店周边解决
+下午｜取车、检查车辆、补充饮水和随车物资
+18:30｜晚餐：西宁市区</x:v>
       </x:c>
       <x:c r="E2" s="32" t="str"/>
       <x:c r="F2" s="32" t="str">
@@ -1355,7 +1337,7 @@
       <x:c r="N2" s="21"/>
       <x:c r="O2" s="21"/>
     </x:row>
-    <x:row r="3" s="1" customFormat="1" ht="142" customHeight="1">
+    <x:row r="3" s="1" customFormat="1" ht="238" customHeight="1">
       <x:c r="A3" s="32" t="str">
         <x:v>D2</x:v>
       </x:c>
@@ -1366,34 +1348,40 @@
         <x:v>西宁</x:v>
       </x:c>
       <x:c r="D3" s="34" t="str">
-        <x:v>09:00 西宁出发，经达坂山方向前往门源
-门源观景后在峨堡镇一带午餐
-下午沿祁连山草原行驶，预计 17:30–18:30 抵达祁连县</x:v>
+        <x:v>09:00｜西宁出发
+↓ 约 2 h 30 min
+11:30｜青海湖沿途观景点｜海拔约 3,196 m｜游玩 1 h
+12:30｜午餐：青海湖沿线 / 江西沟｜用餐约 1 h
+13:30｜继续沿湖向西
+15:00｜青海湖西岸合规观景点｜海拔约 3,196 m｜游玩 1 h
+16:00｜出发前往茶卡
+18:00｜抵达茶卡并入住
+18:30｜晚餐：茶卡镇</x:v>
       </x:c>
       <x:c r="E3" s="32" t="str">
-        <x:v>祁连县</x:v>
+        <x:v>茶卡</x:v>
       </x:c>
       <x:c r="F3" s="32" t="str">
-        <x:v>约 280–320 km
-约 5–6 h</x:v>
+        <x:v>约 300–330 km
+约 5–5.5 h</x:v>
       </x:c>
       <x:c r="G3" s="35" t="str">
-        <x:v>喆·非酒店（海北祁连县人民广场店）
-  携程指定日期显示有房，公开页需登录查看结算价
-丽怡酒店（祁连卓尔山景区店）
-  携程同区域房价区间参考
-宜必思尚品酒店（祁连卓尔山景区店）
-  Trip.com 指定日期暂不可订，可后续观察放房</x:v>
+        <x:v>茶卡盐湖天域假日酒店
+  Trip.com 旺季含税参考价；双床、早餐、可免费取消
+柏兰岛酒店
+  Trip.com 同酒店旺季参考价；双床、早餐、供氧
+汉庭酒店（茶卡盐湖店）
+  Trip.com 同酒店旺季参考价</x:v>
       </x:c>
       <x:c r="H3" s="32" t="str">
-        <x:v>约 ¥450–650
-约 ¥500–700
-暂未放房</x:v>
+        <x:v>¥517
+约 ¥650–800
+约 ¥380–480</x:v>
       </x:c>
       <x:c r="I3" s="32" t="str">
         <x:v>舒适型
-舒适型
-舒适型</x:v>
+高档型
+经济型</x:v>
       </x:c>
       <x:c r="J3"/>
       <x:c r="K3"/>
@@ -1402,7 +1390,7 @@
       <x:c r="N3" s="21"/>
       <x:c r="O3" s="21"/>
     </x:row>
-    <x:row r="4" s="1" customFormat="1" ht="168" customHeight="1">
+    <x:row r="4" s="1" customFormat="1" ht="238" customHeight="1">
       <x:c r="A4" s="32" t="str">
         <x:v>D3</x:v>
       </x:c>
@@ -1410,41 +1398,43 @@
         <x:v>46245</x:v>
       </x:c>
       <x:c r="C4" s="32" t="str">
-        <x:v>祁连县</x:v>
+        <x:v>茶卡</x:v>
       </x:c>
       <x:c r="D4" s="34" t="str">
-        <x:v>09:00 祁连县出发，经默勒草原或刚察方向进入青海湖北岸
-沿青海湖北岸、西岸行驶，选择 1–2 处湖边点位停留
-在刚察、黑马河或环湖西路一带用餐，预计 19:00–20:00 抵达茶卡</x:v>
+        <x:v>09:00｜茶卡酒店出发
+09:20｜茶卡盐湖｜海拔约 3,059 m｜游玩 3 h
+12:20｜返回茶卡镇
+12:40｜午餐：茶卡镇｜用餐约 1 h
+13:40｜出发前往德令哈
+↓ 约 3 h 30 min，途中安排休息
+17:10｜抵达德令哈并入住｜海拔约 2,980 m
+17:40｜巴音河沿岸散步｜游玩约 1 h
+19:00｜晚餐：德令哈市区</x:v>
       </x:c>
       <x:c r="E4" s="32" t="str">
-        <x:v>茶卡</x:v>
+        <x:v>德令哈</x:v>
       </x:c>
       <x:c r="F4" s="32" t="str">
-        <x:v>约 430–480 km
-约 7–8 h</x:v>
+        <x:v>约 240–260 km
+约 3.5–4 h</x:v>
       </x:c>
       <x:c r="G4" s="35" t="str">
-        <x:v>茶卡盐湖天域假日酒店
-  Trip.com 含税总价；双床、早餐、可免费取消
-柏兰岛酒店
-  Trip.com 含税总价；双床、早餐、供氧
-茶卡东晨国际酒店
-  Trip.com 含税总价
-汉庭酒店（茶卡盐湖店）
-  Trip.com 含税总价</x:v>
+        <x:v>德令哈昆仑大酒店
+  Trip.com 公开起价参考；停车方便，入住日需重新确认
+德令哈金陵德勒大酒店
+  携程同区域旺季规划区间，入住日需重新确认
+德令哈森元品质酒店
+  携程同区域旺季规划区间，入住日需重新确认</x:v>
       </x:c>
       <x:c r="H4" s="32" t="str">
-        <x:v>¥517
-¥739
-¥459
-¥411</x:v>
+        <x:v>约 ¥420–550
+约 ¥380–550
+约 ¥300–450</x:v>
       </x:c>
       <x:c r="I4" s="32" t="str">
-        <x:v>舒适型
+        <x:v>高档型
 高档型
-舒适型
-经济型</x:v>
+舒适型</x:v>
       </x:c>
       <x:c r="J4"/>
       <x:c r="K4"/>
@@ -1453,7 +1443,7 @@
       <x:c r="N4" s="21"/>
       <x:c r="O4" s="21"/>
     </x:row>
-    <x:row r="5" s="1" customFormat="1" ht="150" customHeight="1">
+    <x:row r="5" s="1" customFormat="1" ht="230" customHeight="1">
       <x:c r="A5" s="32" t="str">
         <x:v>D4</x:v>
       </x:c>
@@ -1461,19 +1451,26 @@
         <x:v>46246</x:v>
       </x:c>
       <x:c r="C5" s="32" t="str">
-        <x:v>茶卡</x:v>
+        <x:v>德令哈</x:v>
       </x:c>
       <x:c r="D5" s="34" t="str">
-        <x:v>09:00 前往茶卡盐湖，游览约 3 小时
-午餐后经德令哈前往大柴旦，中途每约 2 小时休息一次
-傍晚到大柴旦翡翠湖看日落，随后入住大柴旦镇</x:v>
+        <x:v>09:00｜德令哈出发
+↓ 约 2 h 10 min
+11:10｜小柴旦湖合规观景点｜海拔约 3,150 m｜游玩约 40 min
+11:50｜出发前往大柴旦镇
+12:50｜午餐：大柴旦镇｜用餐约 1 h
+13:50｜出发前往翡翠湖
+14:10｜大柴旦翡翠湖｜海拔约 3,148 m｜游玩约 3 h
+17:10｜离开景区
+17:30｜返回大柴旦镇并入住
+18:30｜晚餐：大柴旦镇</x:v>
       </x:c>
       <x:c r="E5" s="32" t="str">
         <x:v>大柴旦</x:v>
       </x:c>
       <x:c r="F5" s="32" t="str">
-        <x:v>约 400–430 km
-约 5.5–6 h</x:v>
+        <x:v>约 210–240 km
+约 3.5–4 h</x:v>
       </x:c>
       <x:c r="G5" s="35" t="str">
         <x:v>大柴旦丽呈华廷酒店（翡翠步行街店）
@@ -1500,7 +1497,7 @@
       <x:c r="N5" s="21"/>
       <x:c r="O5" s="21"/>
     </x:row>
-    <x:row r="6" s="1" customFormat="1" ht="154" customHeight="1">
+    <x:row r="6" s="1" customFormat="1" ht="230" customHeight="1">
       <x:c r="A6" s="32" t="str">
         <x:v>D5</x:v>
       </x:c>
@@ -1511,34 +1508,40 @@
         <x:v>大柴旦</x:v>
       </x:c>
       <x:c r="D6" s="34" t="str">
-        <x:v>09:00 大柴旦出发，沿 G315 向西行驶
-在合规停车区观看 U 型公路和沿途戈壁景观，不在车道内停留拍照
-约 15:00 抵达乌素特水上雅丹，游览至傍晚并在景区周边住宿</x:v>
-      </x:c>
-      <x:c r="E6" s="32" t="str">
-        <x:v>水上雅丹</x:v>
-      </x:c>
+        <x:v>08:30｜大柴旦镇出发
+↓ 约 1 h 30 min
+10:00｜G315 U 型公路合规观景点｜海拔约 2,900 m｜游玩 30 min
+10:30｜继续向西
+12:10｜午餐：沿途服务点 / 随车简餐｜用餐约 50 min
+13:00｜前往乌素特水上雅丹
+13:30｜乌素特水上雅丹｜海拔约 2,675 m｜游玩约 3 h
+16:30｜原路返回大柴旦
+↓ 约 3 h
+19:30｜返回大柴旦镇
+19:45｜晚餐：大柴旦镇</x:v>
+      </x:c>
+      <x:c r="E6" s="32" t="str"/>
       <x:c r="F6" s="32" t="str">
-        <x:v>约 300–340 km
-约 4.5–5 h</x:v>
+        <x:v>约 440–480 km
+约 6.5–7 h</x:v>
       </x:c>
       <x:c r="G6" s="35" t="str">
-        <x:v>乌素特水上雅丹梦幻星空野奢度假酒店
-  Trip.com 同区域含税总价参考
-孤独空间（戈壁）野奢酒店
-  Trip.com 同区域含税总价参考
-乌素特雅丹大酒店（水上雅丹景区店）
-  指定日期暂不接受预订，可后续观察放房</x:v>
+        <x:v>续住大柴旦丽呈华廷酒店（翡翠步行街店）
+  与前一晚连住，减少换酒店；供氧、停车、早餐
+续住大柴旦丽呈翠星酒店
+  与前一晚连住，房价以续住页面为准
+续住全季酒店（大柴旦翡翠步行街店）
+  与前一晚连住，房价以续住页面为准</x:v>
       </x:c>
       <x:c r="H6" s="32" t="str">
-        <x:v>¥486
-¥1,397
-暂不可订</x:v>
+        <x:v>约 ¥900–1,300
+约 ¥700–1,000
+约 ¥750–1,050</x:v>
       </x:c>
       <x:c r="I6" s="32" t="str">
-        <x:v>特色住宿
-野奢营地
-景区酒店</x:v>
+        <x:v>高档型
+高档型
+舒适型</x:v>
       </x:c>
       <x:c r="J6"/>
       <x:c r="K6"/>
@@ -1547,7 +1550,7 @@
       <x:c r="N6" s="21"/>
       <x:c r="O6" s="21"/>
     </x:row>
-    <x:row r="7" s="1" customFormat="1" ht="170" customHeight="1">
+    <x:row r="7" s="1" customFormat="1" ht="230" customHeight="1">
       <x:c r="A7" s="32" t="str">
         <x:v>D6</x:v>
       </x:c>
@@ -1555,19 +1558,25 @@
         <x:v>46248</x:v>
       </x:c>
       <x:c r="C7" s="32" t="str">
-        <x:v>水上雅丹</x:v>
+        <x:v>大柴旦</x:v>
       </x:c>
       <x:c r="D7" s="34" t="str">
-        <x:v>09:00 水上雅丹出发，经雅丹地貌和冷湖方向前往敦煌
-冷湖镇午餐、补给和加油，随后前往黑独山开放区域
-根据路况控制黑独山停留时间，经阿克塞进入甘肃，预计 20:00–21:00 抵达敦煌</x:v>
+        <x:v>08:30｜大柴旦镇出发
+↓ 约 3 h 30 min
+12:00｜午餐：冷湖镇｜用餐、补给和加油约 1 h
+13:00｜出发前往黑独山
+13:40｜黑独山开放区域｜海拔约 2,800 m｜游玩约 1 h 20 min
+15:00｜经阿克塞前往敦煌
+↓ 约 4 h 30 min，途中安排休息
+19:30｜抵达敦煌并入住
+20:00｜晚餐：敦煌市区</x:v>
       </x:c>
       <x:c r="E7" s="32" t="str">
         <x:v>敦煌</x:v>
       </x:c>
       <x:c r="F7" s="32" t="str">
-        <x:v>约 480–520 km
-约 7–8 h</x:v>
+        <x:v>约 520–560 km
+约 7.5–8.5 h</x:v>
       </x:c>
       <x:c r="G7" s="35" t="str">
         <x:v>阳光城舒适PLUS酒店（敦煌沙洲夜市店）
@@ -1598,7 +1607,7 @@
       <x:c r="N7" s="21"/>
       <x:c r="O7" s="21"/>
     </x:row>
-    <x:row r="8" s="1" customFormat="1" ht="132" customHeight="1">
+    <x:row r="8" s="1" customFormat="1" ht="210" customHeight="1">
       <x:c r="A8" s="32" t="str">
         <x:v>D7</x:v>
       </x:c>
@@ -1609,9 +1618,14 @@
         <x:v>敦煌</x:v>
       </x:c>
       <x:c r="D8" s="34" t="str">
-        <x:v>09:00 酒店出发，按实名预约场次游览莫高窟，预留约 4 小时
-午餐后回酒店或市区休息
-约 16:30 前往鸣沙山月牙泉，傍晚看日落，随后可在沙州夜市用餐</x:v>
+        <x:v>09:00｜敦煌酒店出发
+09:30｜莫高窟｜海拔约 1,140 m｜游玩约 4 h
+13:30｜返回市区
+14:00｜午餐：敦煌市区｜用餐约 1 h
+15:00｜酒店休息
+16:30｜出发前往鸣沙山月牙泉
+17:00｜鸣沙山月牙泉｜海拔约 1,130 m｜游玩约 4 h
+21:00｜晚餐：沙州夜市 / 敦煌市区</x:v>
       </x:c>
       <x:c r="E8" s="32" t="str"/>
       <x:c r="F8" s="32" t="str">
@@ -1646,22 +1660,22 @@
         <x:v>西宁</x:v>
       </x:c>
       <x:c r="D9" s="39" t="str">
-        <x:v>西宁—门源—祁连—青海湖北岸/西岸—茶卡—大柴旦—水上雅丹—冷湖—黑独山—敦煌</x:v>
+        <x:v>西宁—青海湖—茶卡—德令哈—小柴旦—大柴旦—G315 U 型公路—水上雅丹—大柴旦—冷湖—黑独山—敦煌</x:v>
       </x:c>
       <x:c r="E9" s="38" t="str">
         <x:v>敦煌</x:v>
       </x:c>
       <x:c r="F9" s="38" t="str">
-        <x:v>约 2,000–2,200 km</x:v>
+        <x:v>约 1,850–2,000 km</x:v>
       </x:c>
       <x:c r="G9" s="39" t="str">
         <x:v>酒店共 7 晚；按 8 人、4 间房计算</x:v>
       </x:c>
       <x:c r="H9" s="38" t="str">
-        <x:v>住宿预算 ¥13,960/团</x:v>
+        <x:v>住宿预算 ¥15,216/团</x:v>
       </x:c>
       <x:c r="I9" s="38" t="str">
-        <x:v>人均住宿 ¥1,745</x:v>
+        <x:v>人均住宿 ¥1,902</x:v>
       </x:c>
       <x:c r="J9"/>
       <x:c r="K9"/>
@@ -1689,9 +1703,9 @@
       <x:c r="N10" s="21"/>
       <x:c r="O10" s="21"/>
     </x:row>
-    <x:row r="11" s="1" customFormat="1" ht="124" customHeight="1">
+    <x:row r="11" s="1" customFormat="1" ht="140" customHeight="1">
       <x:c r="A11" s="41" t="str">
-        <x:v>预订与安全提醒：8 月 9 日为到达日；8 月 10–15 日每天 09:00 出发。 提前确认西宁取车、敦煌异地还车；如租车公司不支持，可改为包车。 莫高窟按实名预约场次安排，预约时间会影响 D7 的具体顺序。 荒漠路段见站加油，提前下载离线地图；G315 不在行车道内停车拍照。 酒店价格于 2026 年 7 月 23 日查询，现作为 8 月旺季参考；入住日已调整，价格和房态需在预订页重新确认。预算按 8 人、4 间、7 晚计算。</x:v>
+        <x:v>预订与安全提醒：日间时间为自驾规划值，受路况、景区预约和实际停留节奏影响；景点海拔均为公开资料约数。8 月 9 日为到达日；普通行程日 09:00 出发，D5、D6 两个长途日 08:30 出发。 提前确认西宁取车、敦煌异地还车；如租车公司不支持，可改为包车。 莫高窟按实名预约场次安排，预约时间会影响 D7 的具体顺序。 D5 游览水上雅丹后返回大柴旦续住；不依赖景区住宿。冷湖仅作 D6 午餐、加油和补给点。 荒漠路段见站加油，提前下载离线地图；G315 不在行车道内停车拍照。 酒店价格于 2026 年 7 月 23 日查询，现作为 8 月旺季参考；入住日已调整，价格和房态需在预订页重新确认。预算按 8 人、4 间、7 晚计算。</x:v>
       </x:c>
       <x:c r="B11" s="41"/>
       <x:c r="C11" s="41"/>
@@ -1719,16 +1733,16 @@
         <x:v>团费合计</x:v>
       </x:c>
       <x:c r="F12" s="43"/>
-      <x:c r="G12" s="53" t="n">
-        <x:f>G48</x:f>
-        <x:v>47381</x:v>
+      <x:c r="G12" s="49" t="n">
+        <x:f>G46</x:f>
+        <x:v>48301</x:v>
       </x:c>
       <x:c r="H12" s="43" t="str">
         <x:v>8 人人均</x:v>
       </x:c>
-      <x:c r="I12" s="53" t="n">
-        <x:f>H48</x:f>
-        <x:v>5923</x:v>
+      <x:c r="I12" s="49" t="n">
+        <x:f>H46</x:f>
+        <x:v>6038</x:v>
       </x:c>
       <x:c r="J12"/>
       <x:c r="K12"/>
@@ -1778,17 +1792,17 @@
       </x:c>
       <x:c r="C14" s="34"/>
       <x:c r="D14" s="34"/>
-      <x:c r="E14" s="49" t="n">
+      <x:c r="E14" s="47" t="n">
         <x:v>450</x:v>
       </x:c>
       <x:c r="F14" s="32" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="G14" s="51" t="n">
+      <x:c r="G14" s="48" t="n">
         <x:f>ROUND(E14*F14,0)</x:f>
         <x:v>6300</x:v>
       </x:c>
-      <x:c r="H14" s="51" t="n">
+      <x:c r="H14" s="48" t="n">
         <x:f>ROUND(G14/8,0)</x:f>
         <x:v>788</x:v>
       </x:c>
@@ -1813,17 +1827,17 @@
       </x:c>
       <x:c r="C15" s="34"/>
       <x:c r="D15" s="34"/>
-      <x:c r="E15" s="49" t="n">
+      <x:c r="E15" s="47" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="F15" s="32" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="G15" s="51" t="n">
+      <x:c r="G15" s="48" t="n">
         <x:f>ROUND(E15*F15,0)</x:f>
         <x:v>700</x:v>
       </x:c>
-      <x:c r="H15" s="51" t="n">
+      <x:c r="H15" s="48" t="n">
         <x:f>ROUND(G15/8,0)</x:f>
         <x:v>88</x:v>
       </x:c>
@@ -1848,17 +1862,17 @@
       </x:c>
       <x:c r="C16" s="34"/>
       <x:c r="D16" s="34"/>
-      <x:c r="E16" s="49" t="n">
+      <x:c r="E16" s="47" t="n">
         <x:v>80</x:v>
       </x:c>
       <x:c r="F16" s="32" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="G16" s="51" t="n">
+      <x:c r="G16" s="48" t="n">
         <x:f>ROUND(E16*F16,0)</x:f>
         <x:v>1120</x:v>
       </x:c>
-      <x:c r="H16" s="51" t="n">
+      <x:c r="H16" s="48" t="n">
         <x:f>ROUND(G16/8,0)</x:f>
         <x:v>140</x:v>
       </x:c>
@@ -1883,17 +1897,17 @@
       </x:c>
       <x:c r="C17" s="34"/>
       <x:c r="D17" s="34"/>
-      <x:c r="E17" s="49" t="n">
+      <x:c r="E17" s="47" t="n">
         <x:v>1000</x:v>
       </x:c>
       <x:c r="F17" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G17" s="51" t="n">
+      <x:c r="G17" s="48" t="n">
         <x:f>ROUND(E17*F17,0)</x:f>
         <x:v>2000</x:v>
       </x:c>
-      <x:c r="H17" s="51" t="n">
+      <x:c r="H17" s="48" t="n">
         <x:f>ROUND(G17/8,0)</x:f>
         <x:v>250</x:v>
       </x:c>
@@ -1908,23 +1922,23 @@
       </x:c>
       <x:c r="B18" s="34" t="str">
         <x:v>燃油费
-2,100 km/辆 × 9.5 L/100km × 2 辆 = 399 L</x:v>
+1,900 km/辆 × 9.5 L/100km × 2 辆 ≈ 361 L</x:v>
       </x:c>
       <x:c r="C18" s="34"/>
       <x:c r="D18" s="34"/>
-      <x:c r="E18" s="49" t="n">
+      <x:c r="E18" s="47" t="n">
         <x:v>7.37</x:v>
       </x:c>
       <x:c r="F18" s="32" t="n">
-        <x:v>399</x:v>
-      </x:c>
-      <x:c r="G18" s="51" t="n">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="G18" s="48" t="n">
         <x:f>ROUND(E18*F18,0)</x:f>
-        <x:v>2941</x:v>
-      </x:c>
-      <x:c r="H18" s="51" t="n">
+        <x:v>2661</x:v>
+      </x:c>
+      <x:c r="H18" s="48" t="n">
         <x:f>ROUND(G18/8,0)</x:f>
-        <x:v>368</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="I18" s="34" t="str">
         <x:v>2026-07-22 青海 92 号汽油 ¥7.37/L
@@ -1937,23 +1951,23 @@
       </x:c>
       <x:c r="B19" s="34" t="str">
         <x:v>高速及路桥费
-¥600/辆 × 2 辆</x:v>
+¥550/辆 × 2 辆</x:v>
       </x:c>
       <x:c r="C19" s="34"/>
       <x:c r="D19" s="34"/>
-      <x:c r="E19" s="49" t="n">
-        <x:v>600</x:v>
+      <x:c r="E19" s="47" t="n">
+        <x:v>550</x:v>
       </x:c>
       <x:c r="F19" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="G19" s="51" t="n">
+      <x:c r="G19" s="48" t="n">
         <x:f>ROUND(E19*F19,0)</x:f>
-        <x:v>1200</x:v>
-      </x:c>
-      <x:c r="H19" s="51" t="n">
+        <x:v>1100</x:v>
+      </x:c>
+      <x:c r="H19" s="48" t="n">
         <x:f>ROUND(G19/8,0)</x:f>
-        <x:v>150</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="I19" s="34" t="str">
         <x:v>按本路线高速占比预留，实际以收费站记录为准</x:v>
@@ -1969,17 +1983,17 @@
       </x:c>
       <x:c r="C20" s="34"/>
       <x:c r="D20" s="34"/>
-      <x:c r="E20" s="49" t="n">
+      <x:c r="E20" s="47" t="n">
         <x:v>200</x:v>
       </x:c>
       <x:c r="F20" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G20" s="51" t="n">
+      <x:c r="G20" s="48" t="n">
         <x:f>ROUND(E20*F20,0)</x:f>
         <x:v>200</x:v>
       </x:c>
-      <x:c r="H20" s="51" t="n">
+      <x:c r="H20" s="48" t="n">
         <x:f>ROUND(G20/8,0)</x:f>
         <x:v>25</x:v>
       </x:c>
@@ -1997,17 +2011,17 @@
       </x:c>
       <x:c r="C21" s="34"/>
       <x:c r="D21" s="34"/>
-      <x:c r="E21" s="49" t="n">
+      <x:c r="E21" s="47" t="n">
         <x:v>331</x:v>
       </x:c>
       <x:c r="F21" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G21" s="51" t="n">
+      <x:c r="G21" s="48" t="n">
         <x:f>ROUND(E21*F21,0)</x:f>
         <x:v>1324</x:v>
       </x:c>
-      <x:c r="H21" s="51" t="n">
+      <x:c r="H21" s="48" t="n">
         <x:f>ROUND(G21/8,0)</x:f>
         <x:v>166</x:v>
       </x:c>
@@ -2020,774 +2034,721 @@
         <x:v>酒店</x:v>
       </x:c>
       <x:c r="B22" s="34" t="str">
-        <x:v>D2 祁连｜喆·非酒店
-¥550/间 × 4 间 × 1 晚</x:v>
+        <x:v>D2 茶卡｜天域假日酒店
+¥517/间 × 4 间 × 1 晚</x:v>
       </x:c>
       <x:c r="C22" s="34"/>
       <x:c r="D22" s="34"/>
-      <x:c r="E22" s="49" t="n">
-        <x:v>550</x:v>
+      <x:c r="E22" s="47" t="n">
+        <x:v>517</x:v>
       </x:c>
       <x:c r="F22" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G22" s="51" t="n">
+      <x:c r="G22" s="48" t="n">
         <x:f>ROUND(E22*F22,0)</x:f>
-        <x:v>2200</x:v>
-      </x:c>
-      <x:c r="H22" s="51" t="n">
+        <x:v>2068</x:v>
+      </x:c>
+      <x:c r="H22" s="48" t="n">
         <x:f>ROUND(G22/8,0)</x:f>
-        <x:v>275</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="I22" s="34" t="str">
-        <x:v>携程指定日期有房；公开页需登录，取区域规划中值</x:v>
+        <x:v>Trip.com 2026-07-23 查询的同酒店旺季含税参考价；入住日需重新确认</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="58" customHeight="1">
-      <x:c r="A23" s="47" t="str">
+      <x:c r="A23" s="32" t="str">
         <x:v>酒店</x:v>
       </x:c>
-      <x:c r="B23" s="48" t="str">
-        <x:v>D3 茶卡｜天域假日酒店
-¥517/间 × 4 间 × 1 晚</x:v>
-      </x:c>
-      <x:c r="C23" s="48"/>
-      <x:c r="D23" s="48"/>
-      <x:c r="E23" s="50" t="n">
-        <x:v>517</x:v>
-      </x:c>
-      <x:c r="F23" s="47" t="n">
+      <x:c r="B23" s="34" t="str">
+        <x:v>D3 德令哈｜昆仑大酒店
+¥450/间 × 4 间 × 1 晚</x:v>
+      </x:c>
+      <x:c r="C23" s="34"/>
+      <x:c r="D23" s="34"/>
+      <x:c r="E23" s="47" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="F23" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G23" s="52" t="n">
+      <x:c r="G23" s="48" t="n">
         <x:f>ROUND(E23*F23,0)</x:f>
-        <x:v>2068</x:v>
-      </x:c>
-      <x:c r="H23" s="52" t="n">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="H23" s="48" t="n">
         <x:f>ROUND(G23/8,0)</x:f>
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="I23" s="48" t="str">
-        <x:v>Trip.com 2026-07-23 查询的同酒店旺季含税参考价；入住日需重新确认</x:v>
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="I23" s="34" t="str">
+        <x:v>Trip.com 2026 页面公开起价约 US$59；按旺季规划值测算，入住日需重新确认
+https://www.trip.com/hotels/delingha-hotel-detail-124236601/de-ling-ha-kun-lun-da-jiu-dian/</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="58" customHeight="1">
-      <x:c r="A24" s="47" t="str">
+      <x:c r="A24" s="32" t="str">
         <x:v>酒店</x:v>
       </x:c>
-      <x:c r="B24" s="48" t="str">
+      <x:c r="B24" s="34" t="str">
         <x:v>D4 大柴旦｜丽呈华廷酒店
 ¥900/间 × 4 间 × 1 晚</x:v>
       </x:c>
-      <x:c r="C24" s="48"/>
-      <x:c r="D24" s="48"/>
-      <x:c r="E24" s="50" t="n">
+      <x:c r="C24" s="34"/>
+      <x:c r="D24" s="34"/>
+      <x:c r="E24" s="47" t="n">
         <x:v>900</x:v>
       </x:c>
-      <x:c r="F24" s="47" t="n">
+      <x:c r="F24" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G24" s="52" t="n">
+      <x:c r="G24" s="48" t="n">
         <x:f>ROUND(E24*F24,0)</x:f>
         <x:v>3600</x:v>
       </x:c>
-      <x:c r="H24" s="52" t="n">
+      <x:c r="H24" s="48" t="n">
         <x:f>ROUND(G24/8,0)</x:f>
         <x:v>450</x:v>
       </x:c>
-      <x:c r="I24" s="48" t="str">
+      <x:c r="I24" s="34" t="str">
         <x:v>携程指定日期有房；公开页需登录，按规划起始价</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="58" customHeight="1">
-      <x:c r="A25" s="47" t="str">
+      <x:c r="A25" s="32" t="str">
         <x:v>酒店</x:v>
       </x:c>
-      <x:c r="B25" s="48" t="str">
-        <x:v>D5 水上雅丹｜梦幻星空野奢酒店
-¥486/间 × 4 间 × 1 晚</x:v>
-      </x:c>
-      <x:c r="C25" s="48"/>
-      <x:c r="D25" s="48"/>
-      <x:c r="E25" s="50" t="n">
-        <x:v>486</x:v>
-      </x:c>
-      <x:c r="F25" s="47" t="n">
+      <x:c r="B25" s="34" t="str">
+        <x:v>D5 大柴旦续住｜丽呈华廷酒店
+¥900/间 × 4 间 × 1 晚</x:v>
+      </x:c>
+      <x:c r="C25" s="34"/>
+      <x:c r="D25" s="34"/>
+      <x:c r="E25" s="47" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="F25" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G25" s="52" t="n">
+      <x:c r="G25" s="48" t="n">
         <x:f>ROUND(E25*F25,0)</x:f>
-        <x:v>1944</x:v>
-      </x:c>
-      <x:c r="H25" s="52" t="n">
+        <x:v>3600</x:v>
+      </x:c>
+      <x:c r="H25" s="48" t="n">
         <x:f>ROUND(G25/8,0)</x:f>
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="I25" s="48" t="str">
-        <x:v>Trip.com 同区域含税公开价参考</x:v>
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I25" s="34" t="str">
+        <x:v>按前一晚同酒店续住测算；避免依赖水上雅丹景区房态</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="58" customHeight="1">
-      <x:c r="A26" s="47" t="str">
+      <x:c r="A26" s="32" t="str">
         <x:v>酒店</x:v>
       </x:c>
-      <x:c r="B26" s="48" t="str">
+      <x:c r="B26" s="34" t="str">
         <x:v>D6 敦煌｜阳光城舒适 PLUS
 ¥353/间 × 4 间 × 1 晚</x:v>
       </x:c>
-      <x:c r="C26" s="48"/>
-      <x:c r="D26" s="48"/>
-      <x:c r="E26" s="50" t="n">
+      <x:c r="C26" s="34"/>
+      <x:c r="D26" s="34"/>
+      <x:c r="E26" s="47" t="n">
         <x:v>353</x:v>
       </x:c>
-      <x:c r="F26" s="47" t="n">
+      <x:c r="F26" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G26" s="52" t="n">
+      <x:c r="G26" s="48" t="n">
         <x:f>ROUND(E26*F26,0)</x:f>
         <x:v>1412</x:v>
       </x:c>
-      <x:c r="H26" s="52" t="n">
+      <x:c r="H26" s="48" t="n">
         <x:f>ROUND(G26/8,0)</x:f>
         <x:v>177</x:v>
       </x:c>
-      <x:c r="I26" s="48" t="str">
+      <x:c r="I26" s="34" t="str">
         <x:v>Trip.com 2026-07-23 查询的同酒店旺季含税参考价；入住日需重新确认</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="58" customHeight="1">
-      <x:c r="A27" s="47" t="str">
+      <x:c r="A27" s="32" t="str">
         <x:v>酒店</x:v>
       </x:c>
-      <x:c r="B27" s="48" t="str">
+      <x:c r="B27" s="34" t="str">
         <x:v>D7 敦煌续住｜阳光城舒适 PLUS
 ¥353/间 × 4 间 × 1 晚</x:v>
       </x:c>
-      <x:c r="C27" s="48"/>
-      <x:c r="D27" s="48"/>
-      <x:c r="E27" s="50" t="n">
+      <x:c r="C27" s="34"/>
+      <x:c r="D27" s="34"/>
+      <x:c r="E27" s="47" t="n">
         <x:v>353</x:v>
       </x:c>
-      <x:c r="F27" s="47" t="n">
+      <x:c r="F27" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G27" s="52" t="n">
+      <x:c r="G27" s="48" t="n">
         <x:f>ROUND(E27*F27,0)</x:f>
         <x:v>1412</x:v>
       </x:c>
-      <x:c r="H27" s="52" t="n">
+      <x:c r="H27" s="48" t="n">
         <x:f>ROUND(G27/8,0)</x:f>
         <x:v>177</x:v>
       </x:c>
-      <x:c r="I27" s="48" t="str">
+      <x:c r="I27" s="34" t="str">
         <x:v>按同酒店续住一晚测算</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="58" customHeight="1">
-      <x:c r="A28" s="47" t="str">
+      <x:c r="A28" s="32" t="str">
         <x:v>门票及景交</x:v>
       </x:c>
-      <x:c r="B28" s="48" t="str">
-        <x:v>门源沿途观景
-免费公路沿途观景 × 8 人</x:v>
-      </x:c>
-      <x:c r="C28" s="48"/>
-      <x:c r="D28" s="48"/>
-      <x:c r="E28" s="50" t="n">
+      <x:c r="B28" s="34" t="str">
+        <x:v>青海湖沿途公路观景
+不进入二郎剑等收费景区，沿途合规观景 × 8 人</x:v>
+      </x:c>
+      <x:c r="C28" s="34"/>
+      <x:c r="D28" s="34"/>
+      <x:c r="E28" s="47" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F28" s="47" t="n">
+      <x:c r="F28" s="32" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G28" s="52" t="n">
+      <x:c r="G28" s="48" t="n">
         <x:f>ROUND(E28*F28,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H28" s="52" t="n">
+      <x:c r="H28" s="48" t="n">
         <x:f>ROUND(G28/8,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I28" s="48" t="str">
-        <x:v>路线停留点，不进入另收费景区</x:v>
+      <x:c r="I28" s="34" t="str">
+        <x:v>按当前路线规划</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="58" customHeight="1">
-      <x:c r="A29" s="47" t="str">
+      <x:c r="A29" s="32" t="str">
         <x:v>门票及景交</x:v>
       </x:c>
-      <x:c r="B29" s="48" t="str">
-        <x:v>祁连山草原
-免费沿途观景 × 8 人</x:v>
-      </x:c>
-      <x:c r="C29" s="48"/>
-      <x:c r="D29" s="48"/>
-      <x:c r="E29" s="50" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F29" s="47" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G29" s="52" t="n">
-        <x:f>ROUND(E29*F29,0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H29" s="52" t="n">
-        <x:f>ROUND(G29/8,0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I29" s="48" t="str">
-        <x:v>本行程为沿途草原观景</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="58" customHeight="1">
-      <x:c r="A30" s="47" t="str">
-        <x:v>门票及景交</x:v>
-      </x:c>
-      <x:c r="B30" s="48" t="str">
-        <x:v>青海湖北岸/西岸公路观景
-不进入二郎剑等收费景区 × 8 人</x:v>
-      </x:c>
-      <x:c r="C30" s="48"/>
-      <x:c r="D30" s="48"/>
-      <x:c r="E30" s="50" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F30" s="47" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G30" s="52" t="n">
-        <x:f>ROUND(E30*F30,0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H30" s="52" t="n">
-        <x:f>ROUND(G30/8,0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I30" s="48" t="str">
-        <x:v>按当前路线规划</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="58" customHeight="1">
-      <x:c r="A31" s="47" t="str">
-        <x:v>门票及景交</x:v>
-      </x:c>
-      <x:c r="B31" s="48" t="str">
+      <x:c r="B29" s="34" t="str">
         <x:v>茶卡盐湖门票
 ¥60/人 × 8 人</x:v>
       </x:c>
-      <x:c r="C31" s="48"/>
-      <x:c r="D31" s="48"/>
-      <x:c r="E31" s="50" t="n">
+      <x:c r="C29" s="34"/>
+      <x:c r="D29" s="34"/>
+      <x:c r="E29" s="47" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="F31" s="47" t="n">
+      <x:c r="F29" s="32" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G31" s="52" t="n">
-        <x:f>ROUND(E31*F31,0)</x:f>
+      <x:c r="G29" s="48" t="n">
+        <x:f>ROUND(E29*F29,0)</x:f>
         <x:v>480</x:v>
       </x:c>
-      <x:c r="H31" s="52" t="n">
-        <x:f>ROUND(G31/8,0)</x:f>
+      <x:c r="H29" s="48" t="n">
+        <x:f>ROUND(G29/8,0)</x:f>
         <x:v>60</x:v>
       </x:c>
-      <x:c r="I31" s="48" t="str">
+      <x:c r="I29" s="34" t="str">
         <x:v>2026 旺季全价票
 https://www.chakasl.com/pc/introduction/zeme/detail/1051.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="58" customHeight="1">
-      <x:c r="A32" s="47" t="str">
+    <x:row r="30" ht="58" customHeight="1">
+      <x:c r="A30" s="32" t="str">
         <x:v>门票及景交</x:v>
       </x:c>
-      <x:c r="B32" s="48" t="str">
+      <x:c r="B30" s="34" t="str">
         <x:v>茶卡盐湖集散中心摆渡车
 往返 ¥30/人 × 8 人</x:v>
       </x:c>
-      <x:c r="C32" s="48"/>
-      <x:c r="D32" s="48"/>
-      <x:c r="E32" s="50" t="n">
+      <x:c r="C30" s="34"/>
+      <x:c r="D30" s="34"/>
+      <x:c r="E30" s="47" t="n">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="F32" s="47" t="n">
+      <x:c r="F30" s="32" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G32" s="52" t="n">
-        <x:f>ROUND(E32*F32,0)</x:f>
+      <x:c r="G30" s="48" t="n">
+        <x:f>ROUND(E30*F30,0)</x:f>
         <x:v>240</x:v>
       </x:c>
-      <x:c r="H32" s="52" t="n">
-        <x:f>ROUND(G32/8,0)</x:f>
+      <x:c r="H30" s="48" t="n">
+        <x:f>ROUND(G30/8,0)</x:f>
         <x:v>30</x:v>
       </x:c>
-      <x:c r="I32" s="48" t="str">
+      <x:c r="I30" s="34" t="str">
         <x:v>景区官网公开价
 https://www.chakasl.com/pc/introduction/zeme/detail/1051.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="58" customHeight="1">
-      <x:c r="A33" s="47" t="str">
+    <x:row r="31" ht="58" customHeight="1">
+      <x:c r="A31" s="32" t="str">
         <x:v>门票及景交</x:v>
       </x:c>
-      <x:c r="B33" s="48" t="str">
+      <x:c r="B31" s="34" t="str">
         <x:v>茶卡盐湖小火车
 往返 ¥100/人 × 8 人</x:v>
       </x:c>
-      <x:c r="C33" s="48"/>
-      <x:c r="D33" s="48"/>
-      <x:c r="E33" s="50" t="n">
+      <x:c r="C31" s="34"/>
+      <x:c r="D31" s="34"/>
+      <x:c r="E31" s="47" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F33" s="47" t="n">
+      <x:c r="F31" s="32" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G33" s="52" t="n">
-        <x:f>ROUND(E33*F33,0)</x:f>
+      <x:c r="G31" s="48" t="n">
+        <x:f>ROUND(E31*F31,0)</x:f>
         <x:v>800</x:v>
       </x:c>
-      <x:c r="H33" s="52" t="n">
-        <x:f>ROUND(G33/8,0)</x:f>
+      <x:c r="H31" s="48" t="n">
+        <x:f>ROUND(G31/8,0)</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="I33" s="48" t="str">
+      <x:c r="I31" s="34" t="str">
         <x:v>景区官网公开价；如只乘单程可减 ¥50/人
 https://www.chakasl.com/pc/introduction/zeme/detail/1051.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="58" customHeight="1">
-      <x:c r="A34" s="47" t="str">
+    <x:row r="32" ht="58" customHeight="1">
+      <x:c r="A32" s="32" t="str">
         <x:v>门票及景交</x:v>
       </x:c>
-      <x:c r="B34" s="48" t="str">
+      <x:c r="B32" s="34" t="str">
         <x:v>大柴旦翡翠湖门票
 ¥50/人 × 8 人</x:v>
       </x:c>
-      <x:c r="C34" s="48"/>
-      <x:c r="D34" s="48"/>
-      <x:c r="E34" s="50" t="n">
+      <x:c r="C32" s="34"/>
+      <x:c r="D32" s="34"/>
+      <x:c r="E32" s="47" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="F34" s="47" t="n">
+      <x:c r="F32" s="32" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G34" s="52" t="n">
-        <x:f>ROUND(E34*F34,0)</x:f>
+      <x:c r="G32" s="48" t="n">
+        <x:f>ROUND(E32*F32,0)</x:f>
         <x:v>400</x:v>
       </x:c>
-      <x:c r="H34" s="52" t="n">
-        <x:f>ROUND(G34/8,0)</x:f>
+      <x:c r="H32" s="48" t="n">
+        <x:f>ROUND(G32/8,0)</x:f>
         <x:v>50</x:v>
       </x:c>
-      <x:c r="I34" s="48" t="str">
+      <x:c r="I32" s="34" t="str">
         <x:v>2026 旺季公开价
 https://gs.ctrip.com/html5/you/sight/haixiprefecture120012/4331367.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="58" customHeight="1">
-      <x:c r="A35" s="47" t="str">
+    <x:row r="33" ht="58" customHeight="1">
+      <x:c r="A33" s="32" t="str">
         <x:v>门票及景交</x:v>
       </x:c>
-      <x:c r="B35" s="48" t="str">
+      <x:c r="B33" s="34" t="str">
         <x:v>大柴旦翡翠湖观光小火车
 ¥60/人 × 8 人</x:v>
       </x:c>
-      <x:c r="C35" s="48"/>
-      <x:c r="D35" s="48"/>
-      <x:c r="E35" s="50" t="n">
+      <x:c r="C33" s="34"/>
+      <x:c r="D33" s="34"/>
+      <x:c r="E33" s="47" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="F35" s="47" t="n">
+      <x:c r="F33" s="32" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G35" s="52" t="n">
+      <x:c r="G33" s="48" t="n">
+        <x:f>ROUND(E33*F33,0)</x:f>
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="H33" s="48" t="n">
+        <x:f>ROUND(G33/8,0)</x:f>
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="I33" s="34" t="str">
+        <x:v>2026 公开价
+https://gs.ctrip.com/html5/you/sight/haixiprefecture120012/4331367.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="58" customHeight="1">
+      <x:c r="A34" s="32" t="str">
+        <x:v>门票及景交</x:v>
+      </x:c>
+      <x:c r="B34" s="34" t="str">
+        <x:v>G315 U 型公路
+免费公路观景 × 8 人</x:v>
+      </x:c>
+      <x:c r="C34" s="34"/>
+      <x:c r="D34" s="34"/>
+      <x:c r="E34" s="47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F34" s="32" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G34" s="48" t="n">
+        <x:f>ROUND(E34*F34,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H34" s="48" t="n">
+        <x:f>ROUND(G34/8,0)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I34" s="34" t="str">
+        <x:v>仅在合规停车区停留</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="58" customHeight="1">
+      <x:c r="A35" s="32" t="str">
+        <x:v>门票及景交</x:v>
+      </x:c>
+      <x:c r="B35" s="34" t="str">
+        <x:v>乌素特水上雅丹门票
+¥60/人 × 8 人</x:v>
+      </x:c>
+      <x:c r="C35" s="34"/>
+      <x:c r="D35" s="34"/>
+      <x:c r="E35" s="47" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F35" s="32" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G35" s="48" t="n">
         <x:f>ROUND(E35*F35,0)</x:f>
         <x:v>480</x:v>
       </x:c>
-      <x:c r="H35" s="52" t="n">
+      <x:c r="H35" s="48" t="n">
         <x:f>ROUND(G35/8,0)</x:f>
         <x:v>60</x:v>
       </x:c>
-      <x:c r="I35" s="48" t="str">
-        <x:v>2026 公开价
-https://gs.ctrip.com/html5/you/sight/haixiprefecture120012/4331367.html</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" ht="58" customHeight="1">
-      <x:c r="A36" s="47" t="str">
-        <x:v>门票及景交</x:v>
-      </x:c>
-      <x:c r="B36" s="48" t="str">
-        <x:v>G315 U 型公路
-免费公路观景 × 8 人</x:v>
-      </x:c>
-      <x:c r="C36" s="48"/>
-      <x:c r="D36" s="48"/>
-      <x:c r="E36" s="50" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F36" s="47" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G36" s="52" t="n">
-        <x:f>ROUND(E36*F36,0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H36" s="52" t="n">
-        <x:f>ROUND(G36/8,0)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I36" s="48" t="str">
-        <x:v>仅在合规停车区停留</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" ht="58" customHeight="1">
-      <x:c r="A37" s="47" t="str">
-        <x:v>门票及景交</x:v>
-      </x:c>
-      <x:c r="B37" s="48" t="str">
-        <x:v>乌素特水上雅丹门票
-¥60/人 × 8 人</x:v>
-      </x:c>
-      <x:c r="C37" s="48"/>
-      <x:c r="D37" s="48"/>
-      <x:c r="E37" s="50" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F37" s="47" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G37" s="52" t="n">
-        <x:f>ROUND(E37*F37,0)</x:f>
-        <x:v>480</x:v>
-      </x:c>
-      <x:c r="H37" s="52" t="n">
-        <x:f>ROUND(G37/8,0)</x:f>
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I37" s="48" t="str">
+      <x:c r="I35" s="34" t="str">
         <x:v>景区官网公开价
 https://www.wusuteyadan.com/list/ticket.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="58" customHeight="1">
-      <x:c r="A38" s="47" t="str">
+    <x:row r="36" ht="58" customHeight="1">
+      <x:c r="A36" s="32" t="str">
         <x:v>门票及景交</x:v>
       </x:c>
-      <x:c r="B38" s="48" t="str">
+      <x:c r="B36" s="34" t="str">
         <x:v>乌素特水上雅丹观光车
 往返 ¥60/人 × 8 人</x:v>
       </x:c>
-      <x:c r="C38" s="48"/>
-      <x:c r="D38" s="48"/>
-      <x:c r="E38" s="50" t="n">
+      <x:c r="C36" s="34"/>
+      <x:c r="D36" s="34"/>
+      <x:c r="E36" s="47" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="F38" s="47" t="n">
+      <x:c r="F36" s="32" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G38" s="52" t="n">
-        <x:f>ROUND(E38*F38,0)</x:f>
+      <x:c r="G36" s="48" t="n">
+        <x:f>ROUND(E36*F36,0)</x:f>
         <x:v>480</x:v>
       </x:c>
-      <x:c r="H38" s="52" t="n">
-        <x:f>ROUND(G38/8,0)</x:f>
+      <x:c r="H36" s="48" t="n">
+        <x:f>ROUND(G36/8,0)</x:f>
         <x:v>60</x:v>
       </x:c>
-      <x:c r="I38" s="48" t="str">
+      <x:c r="I36" s="34" t="str">
         <x:v>景区官网公开价
 https://www.wusuteyadan.com/list/ticket.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="58" customHeight="1">
-      <x:c r="A39" s="47" t="str">
+    <x:row r="37" ht="58" customHeight="1">
+      <x:c r="A37" s="32" t="str">
         <x:v>门票及景交</x:v>
       </x:c>
-      <x:c r="B39" s="48" t="str">
+      <x:c r="B37" s="34" t="str">
         <x:v>冷湖/黑独山开放区域
 免费开放区域 × 8 人</x:v>
       </x:c>
-      <x:c r="C39" s="48"/>
-      <x:c r="D39" s="48"/>
-      <x:c r="E39" s="50" t="n">
+      <x:c r="C37" s="34"/>
+      <x:c r="D37" s="34"/>
+      <x:c r="E37" s="47" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F39" s="47" t="n">
+      <x:c r="F37" s="32" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G39" s="52" t="n">
-        <x:f>ROUND(E39*F39,0)</x:f>
+      <x:c r="G37" s="48" t="n">
+        <x:f>ROUND(E37*F37,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H39" s="52" t="n">
-        <x:f>ROUND(G39/8,0)</x:f>
+      <x:c r="H37" s="48" t="n">
+        <x:f>ROUND(G37/8,0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I39" s="48" t="str">
+      <x:c r="I37" s="34" t="str">
         <x:v>不含当地临时管控或商业接驳</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="58" customHeight="1">
-      <x:c r="A40" s="47" t="str">
+    <x:row r="38" ht="58" customHeight="1">
+      <x:c r="A38" s="32" t="str">
         <x:v>门票及景交</x:v>
       </x:c>
-      <x:c r="B40" s="48" t="str">
+      <x:c r="B38" s="34" t="str">
         <x:v>莫高窟 A 类常规票
 ¥238/人 × 8 人</x:v>
       </x:c>
-      <x:c r="C40" s="48"/>
-      <x:c r="D40" s="48"/>
-      <x:c r="E40" s="50" t="n">
+      <x:c r="C38" s="34"/>
+      <x:c r="D38" s="34"/>
+      <x:c r="E38" s="47" t="n">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="F40" s="47" t="n">
+      <x:c r="F38" s="32" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G40" s="52" t="n">
-        <x:f>ROUND(E40*F40,0)</x:f>
+      <x:c r="G38" s="48" t="n">
+        <x:f>ROUND(E38*F38,0)</x:f>
         <x:v>1904</x:v>
       </x:c>
-      <x:c r="H40" s="52" t="n">
-        <x:f>ROUND(G40/8,0)</x:f>
+      <x:c r="H38" s="48" t="n">
+        <x:f>ROUND(G38/8,0)</x:f>
         <x:v>238</x:v>
       </x:c>
-      <x:c r="I40" s="48" t="str">
+      <x:c r="I38" s="34" t="str">
         <x:v>2026 旺季 A 类票；含数字电影、8 个洞窟、讲解和往返摆渡
 https://www.dunhuangcaves.org/skxl/mgk.htm</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="58" customHeight="1">
-      <x:c r="A41" s="47" t="str">
+    <x:row r="39" ht="58" customHeight="1">
+      <x:c r="A39" s="32" t="str">
         <x:v>门票及景交</x:v>
       </x:c>
-      <x:c r="B41" s="48" t="str">
+      <x:c r="B39" s="34" t="str">
         <x:v>鸣沙山月牙泉门票
 ¥110/人 × 8 人</x:v>
       </x:c>
-      <x:c r="C41" s="48"/>
-      <x:c r="D41" s="48"/>
-      <x:c r="E41" s="50" t="n">
+      <x:c r="C39" s="34"/>
+      <x:c r="D39" s="34"/>
+      <x:c r="E39" s="47" t="n">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="F41" s="47" t="n">
+      <x:c r="F39" s="32" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G41" s="52" t="n">
-        <x:f>ROUND(E41*F41,0)</x:f>
+      <x:c r="G39" s="48" t="n">
+        <x:f>ROUND(E39*F39,0)</x:f>
         <x:v>880</x:v>
       </x:c>
-      <x:c r="H41" s="52" t="n">
-        <x:f>ROUND(G41/8,0)</x:f>
+      <x:c r="H39" s="48" t="n">
+        <x:f>ROUND(G39/8,0)</x:f>
         <x:v>110</x:v>
       </x:c>
-      <x:c r="I41" s="48" t="str">
+      <x:c r="I39" s="34" t="str">
         <x:v>2026 公开平台票价；骑骆驼等项目不计入基础预算
 https://gs.ctrip.com/html5/you/sight/dunhuang8/1563.html</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="58" customHeight="1">
-      <x:c r="A42" s="47" t="str">
+    <x:row r="40" ht="58" customHeight="1">
+      <x:c r="A40" s="32" t="str">
         <x:v>餐饮</x:v>
       </x:c>
-      <x:c r="B42" s="48" t="str">
+      <x:c r="B40" s="34" t="str">
         <x:v>早餐补充
 ¥20/人/天 × 8 人 × 7 天</x:v>
       </x:c>
-      <x:c r="C42" s="48"/>
-      <x:c r="D42" s="48"/>
-      <x:c r="E42" s="50" t="n">
+      <x:c r="C40" s="34"/>
+      <x:c r="D40" s="34"/>
+      <x:c r="E40" s="47" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F42" s="47" t="n">
+      <x:c r="F40" s="32" t="n">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G42" s="52" t="n">
-        <x:f>ROUND(E42*F42,0)</x:f>
+      <x:c r="G40" s="48" t="n">
+        <x:f>ROUND(E40*F40,0)</x:f>
         <x:v>1120</x:v>
       </x:c>
-      <x:c r="H42" s="52" t="n">
-        <x:f>ROUND(G42/8,0)</x:f>
+      <x:c r="H40" s="48" t="n">
+        <x:f>ROUND(G40/8,0)</x:f>
         <x:v>140</x:v>
       </x:c>
-      <x:c r="I42" s="48" t="str">
+      <x:c r="I40" s="34" t="str">
         <x:v>部分酒店含早，按全程保守预留</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="58" customHeight="1">
-      <x:c r="A43" s="47" t="str">
+    <x:row r="41" ht="58" customHeight="1">
+      <x:c r="A41" s="32" t="str">
         <x:v>餐饮</x:v>
       </x:c>
-      <x:c r="B43" s="48" t="str">
+      <x:c r="B41" s="34" t="str">
         <x:v>午餐
 ¥50/人/天 × 8 人 × 7 天</x:v>
       </x:c>
-      <x:c r="C43" s="48"/>
-      <x:c r="D43" s="48"/>
-      <x:c r="E43" s="50" t="n">
+      <x:c r="C41" s="34"/>
+      <x:c r="D41" s="34"/>
+      <x:c r="E41" s="47" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="F43" s="47" t="n">
+      <x:c r="F41" s="32" t="n">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G43" s="52" t="n">
-        <x:f>ROUND(E43*F43,0)</x:f>
+      <x:c r="G41" s="48" t="n">
+        <x:f>ROUND(E41*F41,0)</x:f>
         <x:v>2800</x:v>
       </x:c>
-      <x:c r="H43" s="52" t="n">
-        <x:f>ROUND(G43/8,0)</x:f>
+      <x:c r="H41" s="48" t="n">
+        <x:f>ROUND(G41/8,0)</x:f>
         <x:v>350</x:v>
       </x:c>
-      <x:c r="I43" s="48" t="str">
+      <x:c r="I41" s="34" t="str">
         <x:v>西北公路餐饮规划值</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="58" customHeight="1">
-      <x:c r="A44" s="47" t="str">
+    <x:row r="42" ht="58" customHeight="1">
+      <x:c r="A42" s="32" t="str">
         <x:v>餐饮</x:v>
       </x:c>
-      <x:c r="B44" s="48" t="str">
+      <x:c r="B42" s="34" t="str">
         <x:v>晚餐
 ¥70/人/天 × 8 人 × 7 天</x:v>
       </x:c>
-      <x:c r="C44" s="48"/>
-      <x:c r="D44" s="48"/>
-      <x:c r="E44" s="50" t="n">
+      <x:c r="C42" s="34"/>
+      <x:c r="D42" s="34"/>
+      <x:c r="E42" s="47" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="F44" s="47" t="n">
+      <x:c r="F42" s="32" t="n">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G44" s="52" t="n">
-        <x:f>ROUND(E44*F44,0)</x:f>
+      <x:c r="G42" s="48" t="n">
+        <x:f>ROUND(E42*F42,0)</x:f>
         <x:v>3920</x:v>
       </x:c>
-      <x:c r="H44" s="52" t="n">
-        <x:f>ROUND(G44/8,0)</x:f>
+      <x:c r="H42" s="48" t="n">
+        <x:f>ROUND(G42/8,0)</x:f>
         <x:v>490</x:v>
       </x:c>
-      <x:c r="I44" s="48" t="str">
+      <x:c r="I42" s="34" t="str">
         <x:v>西北城市及景区周边餐饮规划值</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="58" customHeight="1">
-      <x:c r="A45" s="47" t="str">
+    <x:row r="43" ht="58" customHeight="1">
+      <x:c r="A43" s="32" t="str">
         <x:v>餐饮</x:v>
       </x:c>
-      <x:c r="B45" s="48" t="str">
+      <x:c r="B43" s="34" t="str">
         <x:v>饮水及零食
 ¥20/人/天 × 8 人 × 7 天</x:v>
       </x:c>
-      <x:c r="C45" s="48"/>
-      <x:c r="D45" s="48"/>
-      <x:c r="E45" s="50" t="n">
+      <x:c r="C43" s="34"/>
+      <x:c r="D43" s="34"/>
+      <x:c r="E43" s="47" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="F45" s="47" t="n">
+      <x:c r="F43" s="32" t="n">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G45" s="52" t="n">
-        <x:f>ROUND(E45*F45,0)</x:f>
+      <x:c r="G43" s="48" t="n">
+        <x:f>ROUND(E43*F43,0)</x:f>
         <x:v>1120</x:v>
       </x:c>
-      <x:c r="H45" s="52" t="n">
-        <x:f>ROUND(G45/8,0)</x:f>
+      <x:c r="H43" s="48" t="n">
+        <x:f>ROUND(G43/8,0)</x:f>
         <x:v>140</x:v>
       </x:c>
-      <x:c r="I45" s="48" t="str">
+      <x:c r="I43" s="34" t="str">
         <x:v>长途驾驶补给预留</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="58" customHeight="1">
-      <x:c r="A46" s="47" t="str">
+    <x:row r="44" ht="58" customHeight="1">
+      <x:c r="A44" s="32" t="str">
         <x:v>物资及机动</x:v>
       </x:c>
-      <x:c r="B46" s="48" t="str">
+      <x:c r="B44" s="34" t="str">
         <x:v>氧气、常用药和应急用品
 ¥200/人 × 8 人</x:v>
       </x:c>
-      <x:c r="C46" s="48"/>
-      <x:c r="D46" s="48"/>
-      <x:c r="E46" s="50" t="n">
+      <x:c r="C44" s="34"/>
+      <x:c r="D44" s="34"/>
+      <x:c r="E44" s="47" t="n">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="F46" s="47" t="n">
+      <x:c r="F44" s="32" t="n">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="G44" s="48" t="n">
+        <x:f>ROUND(E44*F44,0)</x:f>
+        <x:v>1600</x:v>
+      </x:c>
+      <x:c r="H44" s="48" t="n">
+        <x:f>ROUND(G44/8,0)</x:f>
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="I44" s="34" t="str">
+        <x:v>高原及荒漠路段随车物资预留</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="58" customHeight="1">
+      <x:c r="A45" s="32" t="str">
+        <x:v>物资及机动</x:v>
+      </x:c>
+      <x:c r="B45" s="34" t="str">
+        <x:v>机动金
+上述费用小计的约 5%</x:v>
+      </x:c>
+      <x:c r="C45" s="34"/>
+      <x:c r="D45" s="34"/>
+      <x:c r="E45" s="50" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="F45" s="32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G45" s="48" t="n">
+        <x:f>ROUND(SUM(G14:G44)*E45,0)</x:f>
+        <x:v>2300</x:v>
+      </x:c>
+      <x:c r="H45" s="48" t="n">
+        <x:f>ROUND(G45/8,0)</x:f>
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="I45" s="34" t="str">
+        <x:v>用于价格波动、临时补给和小额改签</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="42" customHeight="1">
+      <x:c r="A46" s="38" t="str">
+        <x:v>费用合计</x:v>
+      </x:c>
+      <x:c r="B46" s="38" t="str">
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="C46" s="38"/>
+      <x:c r="D46" s="38"/>
+      <x:c r="E46" s="38"/>
+      <x:c r="F46" s="38"/>
       <x:c r="G46" s="52" t="n">
-        <x:f>ROUND(E46*F46,0)</x:f>
-        <x:v>1600</x:v>
+        <x:f>SUM(G14:G45)</x:f>
+        <x:v>48301</x:v>
       </x:c>
       <x:c r="H46" s="52" t="n">
         <x:f>ROUND(G46/8,0)</x:f>
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="I46" s="48" t="str">
-        <x:v>高原及荒漠路段随车物资预留</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" ht="58" customHeight="1">
-      <x:c r="A47" s="47" t="str">
-        <x:v>物资及机动</x:v>
-      </x:c>
-      <x:c r="B47" s="48" t="str">
-        <x:v>机动金
-上述费用小计的约 5%</x:v>
-      </x:c>
-      <x:c r="C47" s="48"/>
-      <x:c r="D47" s="48"/>
-      <x:c r="E47" s="54" t="n">
-        <x:v>0.05</x:v>
-      </x:c>
-      <x:c r="F47" s="47" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G47" s="52" t="n">
-        <x:f>ROUND(SUM(G14:G46)*E47,0)</x:f>
-        <x:v>2256</x:v>
-      </x:c>
-      <x:c r="H47" s="52" t="n">
-        <x:f>ROUND(G47/8,0)</x:f>
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="I47" s="48" t="str">
-        <x:v>用于价格波动、临时补给和小额改签</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" ht="42" customHeight="1">
-      <x:c r="A48" s="57" t="str">
-        <x:v>费用合计</x:v>
-      </x:c>
-      <x:c r="B48" s="57" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="C48" s="57"/>
-      <x:c r="D48" s="57"/>
-      <x:c r="E48" s="57"/>
-      <x:c r="F48" s="57"/>
-      <x:c r="G48" s="58" t="n">
-        <x:f>SUM(G14:G47)</x:f>
-        <x:v>47381</x:v>
-      </x:c>
-      <x:c r="H48" s="58" t="n">
-        <x:f>ROUND(G48/8,0)</x:f>
-        <x:v>5923</x:v>
-      </x:c>
-      <x:c r="I48" s="57" t="str">
+        <x:v>6038</x:v>
+      </x:c>
+      <x:c r="I46" s="38" t="str">
         <x:v>按 8 人测算</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="64" customHeight="1">
-      <x:c r="A49" s="60" t="str">
+    <x:row r="47" ht="64" customHeight="1">
+      <x:c r="A47" s="41" t="str">
         <x:v>不含项目：不含往返西宁/敦煌的大交通、个人购物、单房差及未列明的自选娱乐项目。租车与异地还车费必须在下单前以平台结算页重新核验。 自选项目（未计入）：鸣沙山骑骆驼、滑沙、越野车等自选项目、莫高窟特窟票、茶卡盐湖游船、观光塔等自选项目。</x:v>
       </x:c>
-      <x:c r="B49" s="60"/>
-      <x:c r="C49" s="60"/>
-      <x:c r="D49" s="60"/>
-      <x:c r="E49" s="60"/>
-      <x:c r="F49" s="60"/>
-      <x:c r="G49" s="60"/>
-      <x:c r="H49" s="60"/>
-      <x:c r="I49" s="60"/>
-    </x:row>
+      <x:c r="B47" s="41"/>
+      <x:c r="C47" s="41"/>
+      <x:c r="D47" s="41"/>
+      <x:c r="E47" s="41"/>
+      <x:c r="F47" s="41"/>
+      <x:c r="G47" s="41"/>
+      <x:c r="H47" s="41"/>
+      <x:c r="I47" s="41"/>
+    </x:row>
+    <x:row r="48" ht="2" customHeight="1"/>
+    <x:row r="49" ht="2" customHeight="1"/>
     <x:row r="50" ht="2" customHeight="1"/>
     <x:row r="51" ht="2" customHeight="1"/>
     <x:row r="52" ht="2" customHeight="1"/>
@@ -2840,9 +2801,7 @@
     <x:mergeCell ref="B44:D44"/>
     <x:mergeCell ref="B45:D45"/>
     <x:mergeCell ref="B46:D46"/>
-    <x:mergeCell ref="B47:D47"/>
-    <x:mergeCell ref="B48:D48"/>
-    <x:mergeCell ref="A49:I49"/>
+    <x:mergeCell ref="A47:I47"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/青甘大环线7天行程及详细预算.xlsx
+++ b/青甘大环线7天行程及详细预算.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4400d0e2310048f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R30ed84e80c5a47e2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1304,7 +1304,7 @@
 ↓ 约 30–60 min 市内接驳
 抵达后｜酒店办理入住｜西宁海拔约 2,260 m
 午餐｜按实际抵达时间在机场、车站或酒店周边解决
-下午｜取车、检查车辆、补充饮水和随车物资
+下午｜取车、验车、加油，采购饮水、干粮、氧气和常用药
 18:30｜晚餐：西宁市区</x:v>
       </x:c>
       <x:c r="E2" s="32" t="str"/>
@@ -1314,16 +1314,16 @@
       </x:c>
       <x:c r="G2" s="35" t="str">
         <x:v>西宁万枫酒店
-  Trip.com 含税总价；含早餐、可免费取消
+  旺季含税参考价；含早餐、可免费取消
 宜尚酒店（西宁海湖新区万达广场店）
-  Trip.com 含税总价；含早餐、可免费取消
+  预算采用此酒店；含早餐、停车方便
 普同酒店
-  Trip.com 含税总价</x:v>
+  旺季含税参考价</x:v>
       </x:c>
       <x:c r="H2" s="32" t="str">
-        <x:v>¥468
-¥331
-¥398</x:v>
+        <x:v>约 ¥468
+约 ¥331
+约 ¥398</x:v>
       </x:c>
       <x:c r="I2" s="32" t="str">
         <x:v>高档型
@@ -1350,12 +1350,12 @@
       <x:c r="D3" s="34" t="str">
         <x:v>09:00｜西宁出发
 ↓ 约 2 h 30 min
-11:30｜青海湖沿途观景点｜海拔约 3,196 m｜游玩 1 h
-12:30｜午餐：青海湖沿线 / 江西沟｜用餐约 1 h
-13:30｜继续沿湖向西
-15:00｜青海湖西岸合规观景点｜海拔约 3,196 m｜游玩 1 h
+11:30｜青海湖沿途合规观景点｜海拔约 3,196 m｜游玩 1 h
+12:40｜午餐：青海湖沿线 / 江西沟｜用餐约 1 h
+13:40｜继续沿湖南岸、西岸向茶卡
+15:20｜青海湖西岸合规观景点｜海拔约 3,196 m｜游玩约 40 min
 16:00｜出发前往茶卡
-18:00｜抵达茶卡并入住
+18:00｜抵达茶卡镇并入住
 18:30｜晚餐：茶卡镇</x:v>
       </x:c>
       <x:c r="E3" s="32" t="str">
@@ -1367,14 +1367,14 @@
       </x:c>
       <x:c r="G3" s="35" t="str">
         <x:v>茶卡盐湖天域假日酒店
-  Trip.com 旺季含税参考价；双床、早餐、可免费取消
+  预算采用此酒店；双床、早餐、停车方便
 柏兰岛酒店
-  Trip.com 同酒店旺季参考价；双床、早餐、供氧
+  旺季参考区间；双床、早餐、供氧
 汉庭酒店（茶卡盐湖店）
-  Trip.com 同酒店旺季参考价</x:v>
+  旺季参考区间</x:v>
       </x:c>
       <x:c r="H3" s="32" t="str">
-        <x:v>¥517
+        <x:v>约 ¥517
 约 ¥650–800
 约 ¥380–480</x:v>
       </x:c>
@@ -1390,7 +1390,7 @@
       <x:c r="N3" s="21"/>
       <x:c r="O3" s="21"/>
     </x:row>
-    <x:row r="4" s="1" customFormat="1" ht="238" customHeight="1">
+    <x:row r="4" s="1" customFormat="1" ht="280" customHeight="1">
       <x:c r="A4" s="32" t="str">
         <x:v>D3</x:v>
       </x:c>
@@ -1401,35 +1401,37 @@
         <x:v>茶卡</x:v>
       </x:c>
       <x:c r="D4" s="34" t="str">
-        <x:v>09:00｜茶卡酒店出发
-09:20｜茶卡盐湖｜海拔约 3,059 m｜游玩 3 h
-12:20｜返回茶卡镇
-12:40｜午餐：茶卡镇｜用餐约 1 h
-13:40｜出发前往德令哈
-↓ 约 3 h 30 min，途中安排休息
-17:10｜抵达德令哈并入住｜海拔约 2,980 m
-17:40｜巴音河沿岸散步｜游玩约 1 h
-19:00｜晚餐：德令哈市区</x:v>
+        <x:v>08:30｜茶卡酒店出发
+08:50｜茶卡盐湖｜海拔约 3,059 m｜游玩约 2 h 30 min
+11:20｜出发前往德令哈
+13:50｜午餐：德令哈市区｜用餐约 50 min
+14:40｜出发前往小柴旦湖
+16:45｜小柴旦湖合规观景点｜海拔约 3,150 m｜游玩约 30 min
+17:15｜出发前往大柴旦
+18:20｜抵达大柴旦，办理入住 / 简单补给
+18:40｜大柴旦翡翠湖｜海拔约 3,148 m｜游玩约 2 h
+20:40｜返回大柴旦镇
+21:00｜晚餐：大柴旦镇</x:v>
       </x:c>
       <x:c r="E4" s="32" t="str">
-        <x:v>德令哈</x:v>
+        <x:v>大柴旦</x:v>
       </x:c>
       <x:c r="F4" s="32" t="str">
-        <x:v>约 240–260 km
-约 3.5–4 h</x:v>
+        <x:v>约 470–510 km
+约 6.5–7 h</x:v>
       </x:c>
       <x:c r="G4" s="35" t="str">
-        <x:v>德令哈昆仑大酒店
-  Trip.com 公开起价参考；停车方便，入住日需重新确认
-德令哈金陵德勒大酒店
-  携程同区域旺季规划区间，入住日需重新确认
-德令哈森元品质酒店
-  携程同区域旺季规划区间，入住日需重新确认</x:v>
+        <x:v>大柴旦丽呈华廷酒店（翡翠步行街店）
+  预算按 ¥900/间；供氧、停车、早餐
+大柴旦丽呈翠星酒店
+  旺季参考区间
+全季酒店（大柴旦翡翠步行街店）
+  旺季参考区间</x:v>
       </x:c>
       <x:c r="H4" s="32" t="str">
-        <x:v>约 ¥420–550
-约 ¥380–550
-约 ¥300–450</x:v>
+        <x:v>约 ¥900–1,300
+约 ¥700–1,000
+约 ¥750–1,050</x:v>
       </x:c>
       <x:c r="I4" s="32" t="str">
         <x:v>高档型
@@ -1451,116 +1453,9 @@
         <x:v>46246</x:v>
       </x:c>
       <x:c r="C5" s="32" t="str">
-        <x:v>德令哈</x:v>
+        <x:v>大柴旦</x:v>
       </x:c>
       <x:c r="D5" s="34" t="str">
-        <x:v>09:00｜德令哈出发
-↓ 约 2 h 10 min
-11:10｜小柴旦湖合规观景点｜海拔约 3,150 m｜游玩约 40 min
-11:50｜出发前往大柴旦镇
-12:50｜午餐：大柴旦镇｜用餐约 1 h
-13:50｜出发前往翡翠湖
-14:10｜大柴旦翡翠湖｜海拔约 3,148 m｜游玩约 3 h
-17:10｜离开景区
-17:30｜返回大柴旦镇并入住
-18:30｜晚餐：大柴旦镇</x:v>
-      </x:c>
-      <x:c r="E5" s="32" t="str">
-        <x:v>大柴旦</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="str">
-        <x:v>约 210–240 km
-约 3.5–4 h</x:v>
-      </x:c>
-      <x:c r="G5" s="35" t="str">
-        <x:v>大柴旦丽呈华廷酒店（翡翠步行街店）
-  携程指定日期显示有房；供氧、停车、早餐，公开页需登录查看结算价
-大柴旦丽呈翠星酒店
-  携程同区域房价区间参考
-全季酒店（大柴旦翡翠步行街店）
-  携程同区域房价区间参考</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="str">
-        <x:v>约 ¥900–1,300
-约 ¥700–1,000
-约 ¥750–1,050</x:v>
-      </x:c>
-      <x:c r="I5" s="32" t="str">
-        <x:v>高档型
-高档型
-舒适型</x:v>
-      </x:c>
-      <x:c r="J5"/>
-      <x:c r="K5"/>
-      <x:c r="L5" s="20"/>
-      <x:c r="M5" s="21"/>
-      <x:c r="N5" s="21"/>
-      <x:c r="O5" s="21"/>
-    </x:row>
-    <x:row r="6" s="1" customFormat="1" ht="230" customHeight="1">
-      <x:c r="A6" s="32" t="str">
-        <x:v>D5</x:v>
-      </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>46247</x:v>
-      </x:c>
-      <x:c r="C6" s="32" t="str">
-        <x:v>大柴旦</x:v>
-      </x:c>
-      <x:c r="D6" s="34" t="str">
-        <x:v>08:30｜大柴旦镇出发
-↓ 约 1 h 30 min
-10:00｜G315 U 型公路合规观景点｜海拔约 2,900 m｜游玩 30 min
-10:30｜继续向西
-12:10｜午餐：沿途服务点 / 随车简餐｜用餐约 50 min
-13:00｜前往乌素特水上雅丹
-13:30｜乌素特水上雅丹｜海拔约 2,675 m｜游玩约 3 h
-16:30｜原路返回大柴旦
-↓ 约 3 h
-19:30｜返回大柴旦镇
-19:45｜晚餐：大柴旦镇</x:v>
-      </x:c>
-      <x:c r="E6" s="32" t="str"/>
-      <x:c r="F6" s="32" t="str">
-        <x:v>约 440–480 km
-约 6.5–7 h</x:v>
-      </x:c>
-      <x:c r="G6" s="35" t="str">
-        <x:v>续住大柴旦丽呈华廷酒店（翡翠步行街店）
-  与前一晚连住，减少换酒店；供氧、停车、早餐
-续住大柴旦丽呈翠星酒店
-  与前一晚连住，房价以续住页面为准
-续住全季酒店（大柴旦翡翠步行街店）
-  与前一晚连住，房价以续住页面为准</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="str">
-        <x:v>约 ¥900–1,300
-约 ¥700–1,000
-约 ¥750–1,050</x:v>
-      </x:c>
-      <x:c r="I6" s="32" t="str">
-        <x:v>高档型
-高档型
-舒适型</x:v>
-      </x:c>
-      <x:c r="J6"/>
-      <x:c r="K6"/>
-      <x:c r="L6" s="20"/>
-      <x:c r="M6" s="21"/>
-      <x:c r="N6" s="21"/>
-      <x:c r="O6" s="21"/>
-    </x:row>
-    <x:row r="7" s="1" customFormat="1" ht="230" customHeight="1">
-      <x:c r="A7" s="32" t="str">
-        <x:v>D6</x:v>
-      </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>46248</x:v>
-      </x:c>
-      <x:c r="C7" s="32" t="str">
-        <x:v>大柴旦</x:v>
-      </x:c>
-      <x:c r="D7" s="34" t="str">
         <x:v>08:30｜大柴旦镇出发
 ↓ 约 3 h 30 min
 12:00｜午餐：冷湖镇｜用餐、补给和加油约 1 h
@@ -1568,37 +1463,139 @@
 13:40｜黑独山开放区域｜海拔约 2,800 m｜游玩约 1 h 20 min
 15:00｜经阿克塞前往敦煌
 ↓ 约 4 h 30 min，途中安排休息
-19:30｜抵达敦煌并入住
+19:30｜抵达敦煌并入住｜敦煌海拔约 1,140 m
 20:00｜晚餐：敦煌市区</x:v>
       </x:c>
-      <x:c r="E7" s="32" t="str">
+      <x:c r="E5" s="32" t="str">
         <x:v>敦煌</x:v>
       </x:c>
-      <x:c r="F7" s="32" t="str">
-        <x:v>约 520–560 km
+      <x:c r="F5" s="32" t="str">
+        <x:v>约 500–550 km
 约 7.5–8.5 h</x:v>
       </x:c>
-      <x:c r="G7" s="35" t="str">
+      <x:c r="G5" s="35" t="str">
         <x:v>阳光城舒适PLUS酒店（敦煌沙洲夜市店）
-  Trip.com 含税总价；双床、可免费取消
+  预算采用此酒店；双床、可免费取消
 敦煌御龙大酒店
-  Trip.com 含税总价；双床、早餐、可免费取消
+  双床、早餐、可免费取消
 敦煌暮洲·OASIS度假酒店
-  Trip.com 含税总价
+  旺季含税参考价
 敦煌白鹿酒店（沙洲市场店）
-  Trip.com 含税总价</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="str">
-        <x:v>¥353
-¥303
-¥581
-¥212</x:v>
-      </x:c>
-      <x:c r="I7" s="32" t="str">
+  旺季含税参考价</x:v>
+      </x:c>
+      <x:c r="H5" s="32" t="str">
+        <x:v>约 ¥353
+约 ¥303
+约 ¥581
+约 ¥212</x:v>
+      </x:c>
+      <x:c r="I5" s="32" t="str">
         <x:v>舒适型
 舒适型
 度假型
 经济型</x:v>
+      </x:c>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5" s="20"/>
+      <x:c r="M5" s="21"/>
+      <x:c r="N5" s="21"/>
+      <x:c r="O5" s="21"/>
+    </x:row>
+    <x:row r="6" s="1" customFormat="1" ht="240" customHeight="1">
+      <x:c r="A6" s="32" t="str">
+        <x:v>D5</x:v>
+      </x:c>
+      <x:c r="B6" s="33" t="n">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C6" s="32" t="str">
+        <x:v>敦煌</x:v>
+      </x:c>
+      <x:c r="D6" s="34" t="str">
+        <x:v>09:00｜敦煌酒店出发
+09:30｜莫高窟｜海拔约 1,140 m｜游玩约 4 h
+13:30｜返回敦煌市区
+14:00｜午餐：敦煌市区｜用餐约 1 h
+15:00｜酒店休息
+16:30｜出发前往鸣沙山月牙泉
+17:00｜鸣沙山月牙泉｜海拔约 1,130 m｜游玩约 3 h 30 min
+20:30｜离开景区
+21:00｜晚餐：沙州夜市 / 敦煌市区</x:v>
+      </x:c>
+      <x:c r="E6" s="32" t="str">
+        <x:v>敦煌</x:v>
+      </x:c>
+      <x:c r="F6" s="32" t="str">
+        <x:v>约 70–90 km
+约 2 h</x:v>
+      </x:c>
+      <x:c r="G6" s="35" t="str">
+        <x:v>续住阳光城舒适PLUS酒店（敦煌沙洲夜市店）
+  预算采用此酒店，连续住两晚
+续住前一晚其他敦煌酒店
+  避免换酒店，实际以续住页面为准</x:v>
+      </x:c>
+      <x:c r="H6" s="32" t="str">
+        <x:v>约 ¥353
+约 ¥212–581</x:v>
+      </x:c>
+      <x:c r="I6" s="32" t="str">
+        <x:v>舒适型
+经济型—度假型</x:v>
+      </x:c>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6" s="20"/>
+      <x:c r="M6" s="21"/>
+      <x:c r="N6" s="21"/>
+      <x:c r="O6" s="21"/>
+    </x:row>
+    <x:row r="7" s="1" customFormat="1" ht="240" customHeight="1">
+      <x:c r="A7" s="32" t="str">
+        <x:v>D6</x:v>
+      </x:c>
+      <x:c r="B7" s="33" t="n">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C7" s="32" t="str">
+        <x:v>敦煌</x:v>
+      </x:c>
+      <x:c r="D7" s="34" t="str">
+        <x:v>08:40｜敦煌出发
+10:10｜瓜州服务区 / 县城短休｜约 20 min
+12:30｜午餐：随车干粮｜嘉峪关方向服务区休息约 30 min
+13:00｜继续前往张掖七彩丹霞
+15:00｜抵达张掖七彩丹霞｜海拔约 1,850 m
+15:20—20:20｜深度游玩约 5 h，等待日落
+20:20｜日落结束后前往张掖市区
+21:20｜抵达张掖市区并入住
+21:30｜晚餐：张掖市区</x:v>
+      </x:c>
+      <x:c r="E7" s="32" t="str">
+        <x:v>张掖</x:v>
+      </x:c>
+      <x:c r="F7" s="32" t="str">
+        <x:v>约 590–630 km
+约 7–7.5 h</x:v>
+      </x:c>
+      <x:c r="G7" s="35" t="str">
+        <x:v>公航旅·丹霞明珠酒店
+  预算按 ¥350/间；停车方便，入住日需重新确认
+张掖宾馆
+  市区传统酒店，旺季参考区间
+全季酒店（张掖西站店）
+  交通和停车较方便</x:v>
+      </x:c>
+      <x:c r="H7" s="32" t="str">
+        <x:v>约 ¥300–450
+约 ¥350–550
+约 ¥320–480</x:v>
+      </x:c>
+      <x:c r="I7" s="32" t="str">
+        <x:v>高档型
+高档型
+舒适型</x:v>
       </x:c>
       <x:c r="J7"/>
       <x:c r="K7"/>
@@ -1607,7 +1604,7 @@
       <x:c r="N7" s="21"/>
       <x:c r="O7" s="21"/>
     </x:row>
-    <x:row r="8" s="1" customFormat="1" ht="210" customHeight="1">
+    <x:row r="8" s="1" customFormat="1" ht="250" customHeight="1">
       <x:c r="A8" s="32" t="str">
         <x:v>D7</x:v>
       </x:c>
@@ -1615,32 +1612,44 @@
         <x:v>46249</x:v>
       </x:c>
       <x:c r="C8" s="32" t="str">
-        <x:v>敦煌</x:v>
+        <x:v>张掖</x:v>
       </x:c>
       <x:c r="D8" s="34" t="str">
-        <x:v>09:00｜敦煌酒店出发
-09:30｜莫高窟｜海拔约 1,140 m｜游玩约 4 h
-13:30｜返回市区
-14:00｜午餐：敦煌市区｜用餐约 1 h
-15:00｜酒店休息
-16:30｜出发前往鸣沙山月牙泉
-17:00｜鸣沙山月牙泉｜海拔约 1,130 m｜游玩约 4 h
-21:00｜晚餐：沙州夜市 / 敦煌市区</x:v>
-      </x:c>
-      <x:c r="E8" s="32" t="str"/>
+        <x:v>08:00｜张掖出发
+10:10｜扁都口短休｜海拔约 2,800 m｜停留约 20 min
+10:30｜继续前往岗什卡雪峰
+12:10｜抵达岗什卡雪峰游客可达区域｜海拔约 3,700–4,000 m
+12:10｜午餐：随车干粮
+12:40—14:40｜游客区域轻徒步约 2 h，不安排登顶或远端大本营
+14:40—16:10｜休息、拍照并视体力调整
+16:10｜经门源出发返回西宁
+19:10｜抵达西宁市区并入住
+19:30｜晚餐：西宁市区</x:v>
+      </x:c>
+      <x:c r="E8" s="32" t="str">
+        <x:v>西宁</x:v>
+      </x:c>
       <x:c r="F8" s="32" t="str">
-        <x:v>约 50–70 km
-约 1.5 h</x:v>
+        <x:v>约 360–400 km
+约 5.5–6 h</x:v>
       </x:c>
       <x:c r="G8" s="35" t="str">
-        <x:v>续住前一晚敦煌酒店
-  按 8/15–8/16 一晚计算，实际以续住页面为准</x:v>
+        <x:v>宜尚酒店（西宁海湖新区万达广场店）
+  预算采用此酒店；方便次日返程
+西宁万枫酒店
+  旺季参考价；含早餐
+普同酒店
+  旺季含税参考价</x:v>
       </x:c>
       <x:c r="H8" s="32" t="str">
-        <x:v>¥212–581</x:v>
+        <x:v>约 ¥331
+约 ¥468
+约 ¥398</x:v>
       </x:c>
       <x:c r="I8" s="32" t="str">
-        <x:v>经济型—度假型</x:v>
+        <x:v>舒适型
+高档型
+舒适型</x:v>
       </x:c>
       <x:c r="J8"/>
       <x:c r="K8"/>
@@ -1660,22 +1669,22 @@
         <x:v>西宁</x:v>
       </x:c>
       <x:c r="D9" s="39" t="str">
-        <x:v>西宁—青海湖—茶卡—德令哈—小柴旦—大柴旦—G315 U 型公路—水上雅丹—大柴旦—冷湖—黑独山—敦煌</x:v>
+        <x:v>西宁—青海湖—茶卡—德令哈—小柴旦—大柴旦—冷湖—黑独山—敦煌—瓜州—嘉峪关—张掖七彩丹霞—张掖—扁都口—岗什卡雪峰—门源—西宁</x:v>
       </x:c>
       <x:c r="E9" s="38" t="str">
-        <x:v>敦煌</x:v>
+        <x:v>西宁</x:v>
       </x:c>
       <x:c r="F9" s="38" t="str">
-        <x:v>约 1,850–2,000 km</x:v>
+        <x:v>约 2,450–2,600 km</x:v>
       </x:c>
       <x:c r="G9" s="39" t="str">
         <x:v>酒店共 7 晚；按 8 人、4 间房计算</x:v>
       </x:c>
       <x:c r="H9" s="38" t="str">
-        <x:v>住宿预算 ¥15,216/团</x:v>
+        <x:v>住宿预算 ¥12,540/团</x:v>
       </x:c>
       <x:c r="I9" s="38" t="str">
-        <x:v>人均住宿 ¥1,902</x:v>
+        <x:v>人均住宿 ¥1,568</x:v>
       </x:c>
       <x:c r="J9"/>
       <x:c r="K9"/>
@@ -1686,7 +1695,7 @@
     </x:row>
     <x:row r="10" s="1" customFormat="1" ht="58" customHeight="1">
       <x:c r="A10" s="40" t="str">
-        <x:v>预算说明：按 8 人、2 辆 5 座燃油 SUV、4 间房、7 晚测算，不含往返西宁/敦煌的大交通；详细预算逐项列于下方。</x:v>
+        <x:v>预算说明：按 8 人、2 辆 5 座燃油 SUV、4 间房、7 晚测算；车辆租金和酒店采用旺季规划价，最终以预订结算页为准。 不含抵达西宁和离开西宁的大交通；详细人均预算逐项列于下方。</x:v>
       </x:c>
       <x:c r="B10" s="40"/>
       <x:c r="C10" s="40"/>
@@ -1705,7 +1714,7 @@
     </x:row>
     <x:row r="11" s="1" customFormat="1" ht="140" customHeight="1">
       <x:c r="A11" s="41" t="str">
-        <x:v>预订与安全提醒：日间时间为自驾规划值，受路况、景区预约和实际停留节奏影响；景点海拔均为公开资料约数。8 月 9 日为到达日；普通行程日 09:00 出发，D5、D6 两个长途日 08:30 出发。 提前确认西宁取车、敦煌异地还车；如租车公司不支持，可改为包车。 莫高窟按实名预约场次安排，预约时间会影响 D7 的具体顺序。 D5 游览水上雅丹后返回大柴旦续住；不依赖景区住宿。冷湖仅作 D6 午餐、加油和补给点。 荒漠路段见站加油，提前下载离线地图；G315 不在行车道内停车拍照。 酒店价格于 2026 年 7 月 23 日查询，现作为 8 月旺季参考；入住日已调整，价格和房态需在预订页重新确认。预算按 8 人、4 间、7 晚计算。</x:v>
+        <x:v>预订与安全提醒：日间时间为自驾规划值，受路况、景区预约和实际停留节奏影响；景点海拔均为公开资料约数。8 月 9 日为抵达日；D3、D4 为长途日 08:30 出发，D6 按 08:40 出发，D7 按 08:00 出发。 D3 同日包含茶卡盐湖、德令哈午餐、小柴旦湖和翡翠湖，属于全程节奏最紧的一天；若当天延误，优先压缩小柴旦湖停留。 莫高窟按实名预约场次安排，预约时间会影响 D5 的具体顺序。 D6 七彩丹霞按 8 月日落约 20:15 安排，日落后再进张掖市区，晚餐会较晚。 岗什卡只安排游客可达区域轻徒步，不安排登顶、冰川穿越或远端大本营；高海拔不适者留在游客区域休息。 冷湖作为 D4 午餐、加油和补给点，离开黑独山后直接前往敦煌。 荒漠及长途路段见站加油，提前下载离线地图；酒店和租车价格为旺季规划值，需在预订页重新确认。</x:v>
       </x:c>
       <x:c r="B11" s="41"/>
       <x:c r="C11" s="41"/>
@@ -1724,7 +1733,7 @@
     </x:row>
     <x:row r="12" s="1" customFormat="1" ht="34" customHeight="1">
       <x:c r="A12" s="30" t="str">
-        <x:v>8 人详细费用预算（不含往返大交通）</x:v>
+        <x:v>8 人详细费用及人均预算</x:v>
       </x:c>
       <x:c r="B12" s="30"/>
       <x:c r="C12" s="30"/>
@@ -1734,15 +1743,15 @@
       </x:c>
       <x:c r="F12" s="43"/>
       <x:c r="G12" s="49" t="n">
-        <x:f>G46</x:f>
-        <x:v>48301</x:v>
+        <x:f>G45</x:f>
+        <x:v>45831</x:v>
       </x:c>
       <x:c r="H12" s="43" t="str">
         <x:v>8 人人均</x:v>
       </x:c>
       <x:c r="I12" s="49" t="n">
-        <x:f>H46</x:f>
-        <x:v>6038</x:v>
+        <x:f>H45</x:f>
+        <x:v>5729</x:v>
       </x:c>
       <x:c r="J12"/>
       <x:c r="K12"/>
@@ -1807,7 +1816,7 @@
         <x:v>788</x:v>
       </x:c>
       <x:c r="I14" s="34" t="str">
-        <x:v>一嗨西宁公开车型含哈弗 H6；旺季公开市场基准价，精确价需登录
+        <x:v>一嗨西宁公开车型含哈弗 H6；采用暑期旺季规划价，指定日期以结算页为准
 https://www.1hai.cn/c_xining</x:v>
       </x:c>
       <x:c r="J14"/>
@@ -1842,7 +1851,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="I15" s="34" t="str">
-        <x:v>主流租车平台下单费用结构的规划值
+        <x:v>按主流租车平台订单费用结构预留
 https://www.zuche.com/</x:v>
       </x:c>
       <x:c r="J15"/>
@@ -1892,28 +1901,28 @@
         <x:v>租车及车辆</x:v>
       </x:c>
       <x:c r="B17" s="34" t="str">
-        <x:v>西宁取、敦煌还异地还车费
-¥1,000/辆 × 2 辆</x:v>
+        <x:v>燃油费
+2 辆 × 2,500 km/辆 × 9.5 L/100km ≈ 475 L</x:v>
       </x:c>
       <x:c r="C17" s="34"/>
       <x:c r="D17" s="34"/>
       <x:c r="E17" s="47" t="n">
-        <x:v>1000</x:v>
+        <x:v>7.37</x:v>
       </x:c>
       <x:c r="F17" s="32" t="n">
-        <x:v>2</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="G17" s="48" t="n">
         <x:f>ROUND(E17*F17,0)</x:f>
-        <x:v>2000</x:v>
+        <x:v>3501</x:v>
       </x:c>
       <x:c r="H17" s="48" t="n">
         <x:f>ROUND(G17/8,0)</x:f>
-        <x:v>250</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I17" s="34" t="str">
-        <x:v>公开攻略显示约 ¥800–1,200/辆；平台精确报价需登录核验
-https://booking.1hai.cn/order/firstStep</x:v>
+        <x:v>按青海 92 号汽油 ¥7.37/L 的规划基准测算
+https://www.autohome.com.cn/oil/630000.html</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="58" customHeight="1">
@@ -1921,28 +1930,27 @@
         <x:v>租车及车辆</x:v>
       </x:c>
       <x:c r="B18" s="34" t="str">
-        <x:v>燃油费
-1,900 km/辆 × 9.5 L/100km × 2 辆 ≈ 361 L</x:v>
+        <x:v>高速及路桥费
+¥900/辆 × 2 辆；含敦煌—张掖等高速路段预留</x:v>
       </x:c>
       <x:c r="C18" s="34"/>
       <x:c r="D18" s="34"/>
       <x:c r="E18" s="47" t="n">
-        <x:v>7.37</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="F18" s="32" t="n">
-        <x:v>361</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G18" s="48" t="n">
         <x:f>ROUND(E18*F18,0)</x:f>
-        <x:v>2661</x:v>
+        <x:v>1800</x:v>
       </x:c>
       <x:c r="H18" s="48" t="n">
         <x:f>ROUND(G18/8,0)</x:f>
-        <x:v>333</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="I18" s="34" t="str">
-        <x:v>2026-07-22 青海 92 号汽油 ¥7.37/L
-https://www.autohome.com.cn/oil/630000.html</x:v>
+        <x:v>闭环路线规划值，实际以收费站和导航账单为准</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="58" customHeight="1">
@@ -1950,55 +1958,55 @@
         <x:v>租车及车辆</x:v>
       </x:c>
       <x:c r="B19" s="34" t="str">
-        <x:v>高速及路桥费
-¥550/辆 × 2 辆</x:v>
+        <x:v>停车费
+全程两车景区及城市停车合计预留</x:v>
       </x:c>
       <x:c r="C19" s="34"/>
       <x:c r="D19" s="34"/>
       <x:c r="E19" s="47" t="n">
-        <x:v>550</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="F19" s="32" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G19" s="48" t="n">
         <x:f>ROUND(E19*F19,0)</x:f>
-        <x:v>1100</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="H19" s="48" t="n">
         <x:f>ROUND(G19/8,0)</x:f>
-        <x:v>138</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I19" s="34" t="str">
-        <x:v>按本路线高速占比预留，实际以收费站记录为准</x:v>
+        <x:v>按 7 天、两车规划值</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="58" customHeight="1">
       <x:c r="A20" s="32" t="str">
-        <x:v>租车及车辆</x:v>
+        <x:v>酒店</x:v>
       </x:c>
       <x:c r="B20" s="34" t="str">
-        <x:v>停车费
-全程两车合计预留</x:v>
+        <x:v>D1 西宁｜宜尚酒店
+¥331/间 × 4 间 × 1 晚</x:v>
       </x:c>
       <x:c r="C20" s="34"/>
       <x:c r="D20" s="34"/>
       <x:c r="E20" s="47" t="n">
-        <x:v>200</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="F20" s="32" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G20" s="48" t="n">
         <x:f>ROUND(E20*F20,0)</x:f>
-        <x:v>200</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="H20" s="48" t="n">
         <x:f>ROUND(G20/8,0)</x:f>
-        <x:v>25</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="I20" s="34" t="str">
-        <x:v>茶卡盐湖等景区及城市停车规划值</x:v>
+        <x:v>Trip.com 旺季含税参考价；入住日需重新确认</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="58" customHeight="1">
@@ -2006,27 +2014,27 @@
         <x:v>酒店</x:v>
       </x:c>
       <x:c r="B21" s="34" t="str">
-        <x:v>D1 西宁｜宜尚酒店
-¥331/间 × 4 间 × 1 晚</x:v>
+        <x:v>D2 茶卡｜茶卡盐湖天域假日酒店
+¥517/间 × 4 间 × 1 晚</x:v>
       </x:c>
       <x:c r="C21" s="34"/>
       <x:c r="D21" s="34"/>
       <x:c r="E21" s="47" t="n">
-        <x:v>331</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="F21" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="G21" s="48" t="n">
         <x:f>ROUND(E21*F21,0)</x:f>
-        <x:v>1324</x:v>
+        <x:v>2068</x:v>
       </x:c>
       <x:c r="H21" s="48" t="n">
         <x:f>ROUND(G21/8,0)</x:f>
-        <x:v>166</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="I21" s="34" t="str">
-        <x:v>Trip.com 2026-07-23 查询的同酒店旺季含税参考价；入住日需重新确认</x:v>
+        <x:v>Trip.com 旺季含税参考价；入住日需重新确认</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="58" customHeight="1">
@@ -2034,27 +2042,27 @@
         <x:v>酒店</x:v>
       </x:c>
       <x:c r="B22" s="34" t="str">
-        <x:v>D2 茶卡｜天域假日酒店
-¥517/间 × 4 间 × 1 晚</x:v>
+        <x:v>D3 大柴旦｜丽呈华廷酒店
+¥900/间 × 4 间 × 1 晚</x:v>
       </x:c>
       <x:c r="C22" s="34"/>
       <x:c r="D22" s="34"/>
       <x:c r="E22" s="47" t="n">
-        <x:v>517</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="F22" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="G22" s="48" t="n">
         <x:f>ROUND(E22*F22,0)</x:f>
-        <x:v>2068</x:v>
+        <x:v>3600</x:v>
       </x:c>
       <x:c r="H22" s="48" t="n">
         <x:f>ROUND(G22/8,0)</x:f>
-        <x:v>259</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="I22" s="34" t="str">
-        <x:v>Trip.com 2026-07-23 查询的同酒店旺季含税参考价；入住日需重新确认</x:v>
+        <x:v>携程指定日期显示有房；公开页需登录查看结算价，按规划起始价测算</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="58" customHeight="1">
@@ -2062,28 +2070,27 @@
         <x:v>酒店</x:v>
       </x:c>
       <x:c r="B23" s="34" t="str">
-        <x:v>D3 德令哈｜昆仑大酒店
-¥450/间 × 4 间 × 1 晚</x:v>
+        <x:v>D4 敦煌｜阳光城舒适 PLUS
+¥353/间 × 4 间 × 1 晚</x:v>
       </x:c>
       <x:c r="C23" s="34"/>
       <x:c r="D23" s="34"/>
       <x:c r="E23" s="47" t="n">
-        <x:v>450</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="F23" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="G23" s="48" t="n">
         <x:f>ROUND(E23*F23,0)</x:f>
-        <x:v>1800</x:v>
+        <x:v>1412</x:v>
       </x:c>
       <x:c r="H23" s="48" t="n">
         <x:f>ROUND(G23/8,0)</x:f>
-        <x:v>225</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="I23" s="34" t="str">
-        <x:v>Trip.com 2026 页面公开起价约 US$59；按旺季规划值测算，入住日需重新确认
-https://www.trip.com/hotels/delingha-hotel-detail-124236601/de-ling-ha-kun-lun-da-jiu-dian/</x:v>
+        <x:v>Trip.com 旺季含税参考价；入住日需重新确认</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="58" customHeight="1">
@@ -2091,27 +2098,27 @@
         <x:v>酒店</x:v>
       </x:c>
       <x:c r="B24" s="34" t="str">
-        <x:v>D4 大柴旦｜丽呈华廷酒店
-¥900/间 × 4 间 × 1 晚</x:v>
+        <x:v>D5 敦煌续住｜阳光城舒适 PLUS
+¥353/间 × 4 间 × 1 晚</x:v>
       </x:c>
       <x:c r="C24" s="34"/>
       <x:c r="D24" s="34"/>
       <x:c r="E24" s="47" t="n">
-        <x:v>900</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="F24" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="G24" s="48" t="n">
         <x:f>ROUND(E24*F24,0)</x:f>
-        <x:v>3600</x:v>
+        <x:v>1412</x:v>
       </x:c>
       <x:c r="H24" s="48" t="n">
         <x:f>ROUND(G24/8,0)</x:f>
-        <x:v>450</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="I24" s="34" t="str">
-        <x:v>携程指定日期有房；公开页需登录，按规划起始价</x:v>
+        <x:v>按同酒店续住一晚测算</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="58" customHeight="1">
@@ -2119,27 +2126,27 @@
         <x:v>酒店</x:v>
       </x:c>
       <x:c r="B25" s="34" t="str">
-        <x:v>D5 大柴旦续住｜丽呈华廷酒店
-¥900/间 × 4 间 × 1 晚</x:v>
+        <x:v>D6 张掖｜公航旅·丹霞明珠酒店
+¥350/间 × 4 间 × 1 晚</x:v>
       </x:c>
       <x:c r="C25" s="34"/>
       <x:c r="D25" s="34"/>
       <x:c r="E25" s="47" t="n">
-        <x:v>900</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="F25" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="G25" s="48" t="n">
         <x:f>ROUND(E25*F25,0)</x:f>
-        <x:v>3600</x:v>
+        <x:v>1400</x:v>
       </x:c>
       <x:c r="H25" s="48" t="n">
         <x:f>ROUND(G25/8,0)</x:f>
-        <x:v>450</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="I25" s="34" t="str">
-        <x:v>按前一晚同酒店续住测算；避免依赖水上雅丹景区房态</x:v>
+        <x:v>公开平台约 ¥300–450/间，采用中位规划价；入住日需重新确认</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="58" customHeight="1">
@@ -2147,55 +2154,55 @@
         <x:v>酒店</x:v>
       </x:c>
       <x:c r="B26" s="34" t="str">
-        <x:v>D6 敦煌｜阳光城舒适 PLUS
-¥353/间 × 4 间 × 1 晚</x:v>
+        <x:v>D7 西宁｜宜尚酒店
+¥331/间 × 4 间 × 1 晚</x:v>
       </x:c>
       <x:c r="C26" s="34"/>
       <x:c r="D26" s="34"/>
       <x:c r="E26" s="47" t="n">
-        <x:v>353</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="F26" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="G26" s="48" t="n">
         <x:f>ROUND(E26*F26,0)</x:f>
-        <x:v>1412</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="H26" s="48" t="n">
         <x:f>ROUND(G26/8,0)</x:f>
-        <x:v>177</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="I26" s="34" t="str">
-        <x:v>Trip.com 2026-07-23 查询的同酒店旺季含税参考价；入住日需重新确认</x:v>
+        <x:v>按 D1 同酒店参考价测算；返程当晚入住</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="58" customHeight="1">
       <x:c r="A27" s="32" t="str">
-        <x:v>酒店</x:v>
+        <x:v>门票及景交</x:v>
       </x:c>
       <x:c r="B27" s="34" t="str">
-        <x:v>D7 敦煌续住｜阳光城舒适 PLUS
-¥353/间 × 4 间 × 1 晚</x:v>
+        <x:v>青海湖沿途合规观景
+不进入二郎剑等收费景区 × 8 人</x:v>
       </x:c>
       <x:c r="C27" s="34"/>
       <x:c r="D27" s="34"/>
       <x:c r="E27" s="47" t="n">
-        <x:v>353</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F27" s="32" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G27" s="48" t="n">
         <x:f>ROUND(E27*F27,0)</x:f>
-        <x:v>1412</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H27" s="48" t="n">
         <x:f>ROUND(G27/8,0)</x:f>
-        <x:v>177</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I27" s="34" t="str">
-        <x:v>按同酒店续住一晚测算</x:v>
+        <x:v>按本路线规划；如临时进入收费景区另计</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="58" customHeight="1">
@@ -2203,27 +2210,28 @@
         <x:v>门票及景交</x:v>
       </x:c>
       <x:c r="B28" s="34" t="str">
-        <x:v>青海湖沿途公路观景
-不进入二郎剑等收费景区，沿途合规观景 × 8 人</x:v>
+        <x:v>茶卡盐湖门票
+¥60/人 × 8 人</x:v>
       </x:c>
       <x:c r="C28" s="34"/>
       <x:c r="D28" s="34"/>
       <x:c r="E28" s="47" t="n">
-        <x:v>0</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F28" s="32" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G28" s="48" t="n">
         <x:f>ROUND(E28*F28,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="H28" s="48" t="n">
         <x:f>ROUND(G28/8,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I28" s="34" t="str">
-        <x:v>按当前路线规划</x:v>
+        <x:v>景区官网旺季全价票
+https://www.chakasl.com/pc/introduction/zeme/detail/1051.html</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="58" customHeight="1">
@@ -2231,27 +2239,27 @@
         <x:v>门票及景交</x:v>
       </x:c>
       <x:c r="B29" s="34" t="str">
-        <x:v>茶卡盐湖门票
-¥60/人 × 8 人</x:v>
+        <x:v>茶卡盐湖集散中心摆渡车
+往返 ¥30/人 × 8 人</x:v>
       </x:c>
       <x:c r="C29" s="34"/>
       <x:c r="D29" s="34"/>
       <x:c r="E29" s="47" t="n">
-        <x:v>60</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F29" s="32" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G29" s="48" t="n">
         <x:f>ROUND(E29*F29,0)</x:f>
-        <x:v>480</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="H29" s="48" t="n">
         <x:f>ROUND(G29/8,0)</x:f>
-        <x:v>60</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I29" s="34" t="str">
-        <x:v>2026 旺季全价票
+        <x:v>景区官网公开价
 https://www.chakasl.com/pc/introduction/zeme/detail/1051.html</x:v>
       </x:c>
     </x:row>
@@ -2260,27 +2268,27 @@
         <x:v>门票及景交</x:v>
       </x:c>
       <x:c r="B30" s="34" t="str">
-        <x:v>茶卡盐湖集散中心摆渡车
-往返 ¥30/人 × 8 人</x:v>
+        <x:v>茶卡盐湖小火车
+往返 ¥100/人 × 8 人</x:v>
       </x:c>
       <x:c r="C30" s="34"/>
       <x:c r="D30" s="34"/>
       <x:c r="E30" s="47" t="n">
-        <x:v>30</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F30" s="32" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G30" s="48" t="n">
         <x:f>ROUND(E30*F30,0)</x:f>
-        <x:v>240</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="H30" s="48" t="n">
         <x:f>ROUND(G30/8,0)</x:f>
-        <x:v>30</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I30" s="34" t="str">
-        <x:v>景区官网公开价
+        <x:v>景区官网公开价；若只乘单程可减 ¥50/人
 https://www.chakasl.com/pc/introduction/zeme/detail/1051.html</x:v>
       </x:c>
     </x:row>
@@ -2289,28 +2297,28 @@
         <x:v>门票及景交</x:v>
       </x:c>
       <x:c r="B31" s="34" t="str">
-        <x:v>茶卡盐湖小火车
-往返 ¥100/人 × 8 人</x:v>
+        <x:v>大柴旦翡翠湖门票
+¥50/人 × 8 人</x:v>
       </x:c>
       <x:c r="C31" s="34"/>
       <x:c r="D31" s="34"/>
       <x:c r="E31" s="47" t="n">
-        <x:v>100</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F31" s="32" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G31" s="48" t="n">
         <x:f>ROUND(E31*F31,0)</x:f>
-        <x:v>800</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="H31" s="48" t="n">
         <x:f>ROUND(G31/8,0)</x:f>
-        <x:v>100</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I31" s="34" t="str">
-        <x:v>景区官网公开价；如只乘单程可减 ¥50/人
-https://www.chakasl.com/pc/introduction/zeme/detail/1051.html</x:v>
+        <x:v>公开平台旺季票价
+https://gs.ctrip.com/html5/you/sight/haixiprefecture120012/4331367.html</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="58" customHeight="1">
@@ -2318,27 +2326,27 @@
         <x:v>门票及景交</x:v>
       </x:c>
       <x:c r="B32" s="34" t="str">
-        <x:v>大柴旦翡翠湖门票
-¥50/人 × 8 人</x:v>
+        <x:v>大柴旦翡翠湖观光小火车
+¥60/人 × 8 人</x:v>
       </x:c>
       <x:c r="C32" s="34"/>
       <x:c r="D32" s="34"/>
       <x:c r="E32" s="47" t="n">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F32" s="32" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G32" s="48" t="n">
         <x:f>ROUND(E32*F32,0)</x:f>
-        <x:v>400</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="H32" s="48" t="n">
         <x:f>ROUND(G32/8,0)</x:f>
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I32" s="34" t="str">
-        <x:v>2026 旺季公开价
+        <x:v>公开平台价格
 https://gs.ctrip.com/html5/you/sight/haixiprefecture120012/4331367.html</x:v>
       </x:c>
     </x:row>
@@ -2347,28 +2355,27 @@
         <x:v>门票及景交</x:v>
       </x:c>
       <x:c r="B33" s="34" t="str">
-        <x:v>大柴旦翡翠湖观光小火车
-¥60/人 × 8 人</x:v>
+        <x:v>黑独山开放区域
+免费开放区域 × 8 人</x:v>
       </x:c>
       <x:c r="C33" s="34"/>
       <x:c r="D33" s="34"/>
       <x:c r="E33" s="47" t="n">
-        <x:v>60</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F33" s="32" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G33" s="48" t="n">
         <x:f>ROUND(E33*F33,0)</x:f>
-        <x:v>480</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H33" s="48" t="n">
         <x:f>ROUND(G33/8,0)</x:f>
-        <x:v>60</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I33" s="34" t="str">
-        <x:v>2026 公开价
-https://gs.ctrip.com/html5/you/sight/haixiprefecture120012/4331367.html</x:v>
+        <x:v>不含当地临时管控或商业接驳</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="58" customHeight="1">
@@ -2376,27 +2383,28 @@
         <x:v>门票及景交</x:v>
       </x:c>
       <x:c r="B34" s="34" t="str">
-        <x:v>G315 U 型公路
-免费公路观景 × 8 人</x:v>
+        <x:v>莫高窟 A 类常规票
+¥238/人 × 8 人</x:v>
       </x:c>
       <x:c r="C34" s="34"/>
       <x:c r="D34" s="34"/>
       <x:c r="E34" s="47" t="n">
-        <x:v>0</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="F34" s="32" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G34" s="48" t="n">
         <x:f>ROUND(E34*F34,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>1904</x:v>
       </x:c>
       <x:c r="H34" s="48" t="n">
         <x:f>ROUND(G34/8,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="I34" s="34" t="str">
-        <x:v>仅在合规停车区停留</x:v>
+        <x:v>旺季 A 类票；含数字电影、8 个洞窟、讲解和往返摆渡
+https://www.dunhuangcaves.org/skxl/mgk.htm</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="58" customHeight="1">
@@ -2404,28 +2412,28 @@
         <x:v>门票及景交</x:v>
       </x:c>
       <x:c r="B35" s="34" t="str">
-        <x:v>乌素特水上雅丹门票
-¥60/人 × 8 人</x:v>
+        <x:v>鸣沙山月牙泉门票
+¥110/人 × 8 人</x:v>
       </x:c>
       <x:c r="C35" s="34"/>
       <x:c r="D35" s="34"/>
       <x:c r="E35" s="47" t="n">
-        <x:v>60</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="F35" s="32" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G35" s="48" t="n">
         <x:f>ROUND(E35*F35,0)</x:f>
-        <x:v>480</x:v>
+        <x:v>880</x:v>
       </x:c>
       <x:c r="H35" s="48" t="n">
         <x:f>ROUND(G35/8,0)</x:f>
-        <x:v>60</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="I35" s="34" t="str">
-        <x:v>景区官网公开价
-https://www.wusuteyadan.com/list/ticket.html</x:v>
+        <x:v>公开平台票价；骑骆驼等自选项目不计入基础预算
+https://gs.ctrip.com/html5/you/sight/dunhuang8/1563.html</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="58" customHeight="1">
@@ -2433,28 +2441,28 @@
         <x:v>门票及景交</x:v>
       </x:c>
       <x:c r="B36" s="34" t="str">
-        <x:v>乌素特水上雅丹观光车
-往返 ¥60/人 × 8 人</x:v>
+        <x:v>张掖七彩丹霞门票
+¥70/人 × 8 人</x:v>
       </x:c>
       <x:c r="C36" s="34"/>
       <x:c r="D36" s="34"/>
       <x:c r="E36" s="47" t="n">
-        <x:v>60</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F36" s="32" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G36" s="48" t="n">
         <x:f>ROUND(E36*F36,0)</x:f>
-        <x:v>480</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="H36" s="48" t="n">
         <x:f>ROUND(G36/8,0)</x:f>
-        <x:v>60</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="I36" s="34" t="str">
-        <x:v>景区官网公开价
-https://www.wusuteyadan.com/list/ticket.html</x:v>
+        <x:v>张掖市发展和改革委员会公布的旺季门票价格
+https://www.zhangye.gov.cn/fgw/dzdt/tzgg/202507/t20250711_1426087.html</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="58" customHeight="1">
@@ -2462,27 +2470,28 @@
         <x:v>门票及景交</x:v>
       </x:c>
       <x:c r="B37" s="34" t="str">
-        <x:v>冷湖/黑独山开放区域
-免费开放区域 × 8 人</x:v>
+        <x:v>张掖七彩丹霞观光车
+¥23/人 × 8 人</x:v>
       </x:c>
       <x:c r="C37" s="34"/>
       <x:c r="D37" s="34"/>
       <x:c r="E37" s="47" t="n">
-        <x:v>0</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F37" s="32" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G37" s="48" t="n">
         <x:f>ROUND(E37*F37,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="H37" s="48" t="n">
         <x:f>ROUND(G37/8,0)</x:f>
-        <x:v>0</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="I37" s="34" t="str">
-        <x:v>不含当地临时管控或商业接驳</x:v>
+        <x:v>按公开门票 + 观光车合计 ¥93/人拆分测算
+https://www.zhangye.gov.cn/fgw/dzdt/tzgg/202507/t20250711_1426087.html</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="58" customHeight="1">
@@ -2490,57 +2499,55 @@
         <x:v>门票及景交</x:v>
       </x:c>
       <x:c r="B38" s="34" t="str">
-        <x:v>莫高窟 A 类常规票
-¥238/人 × 8 人</x:v>
+        <x:v>岗什卡雪峰门票/接驳预留
+规划预留 ¥100/人 × 8 人</x:v>
       </x:c>
       <x:c r="C38" s="34"/>
       <x:c r="D38" s="34"/>
       <x:c r="E38" s="47" t="n">
-        <x:v>238</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F38" s="32" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G38" s="48" t="n">
         <x:f>ROUND(E38*F38,0)</x:f>
-        <x:v>1904</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="H38" s="48" t="n">
         <x:f>ROUND(G38/8,0)</x:f>
-        <x:v>238</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I38" s="34" t="str">
-        <x:v>2026 旺季 A 类票；含数字电影、8 个洞窟、讲解和往返摆渡
-https://www.dunhuangcaves.org/skxl/mgk.htm</x:v>
+        <x:v>暂未查到稳定官方固定价，作为门票或当地接驳预留；出发前重新确认</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="58" customHeight="1">
       <x:c r="A39" s="32" t="str">
-        <x:v>门票及景交</x:v>
+        <x:v>餐饮</x:v>
       </x:c>
       <x:c r="B39" s="34" t="str">
-        <x:v>鸣沙山月牙泉门票
-¥110/人 × 8 人</x:v>
+        <x:v>早餐补充
+¥20/人/天 × 8 人 × 7 天</x:v>
       </x:c>
       <x:c r="C39" s="34"/>
       <x:c r="D39" s="34"/>
       <x:c r="E39" s="47" t="n">
-        <x:v>110</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F39" s="32" t="n">
-        <x:v>8</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G39" s="48" t="n">
         <x:f>ROUND(E39*F39,0)</x:f>
-        <x:v>880</x:v>
+        <x:v>1120</x:v>
       </x:c>
       <x:c r="H39" s="48" t="n">
         <x:f>ROUND(G39/8,0)</x:f>
-        <x:v>110</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="I39" s="34" t="str">
-        <x:v>2026 公开平台票价；骑骆驼等项目不计入基础预算
-https://gs.ctrip.com/html5/you/sight/dunhuang8/1563.html</x:v>
+        <x:v>部分酒店含早，按全程保守预留</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="58" customHeight="1">
@@ -2548,27 +2555,27 @@
         <x:v>餐饮</x:v>
       </x:c>
       <x:c r="B40" s="34" t="str">
-        <x:v>早餐补充
-¥20/人/天 × 8 人 × 7 天</x:v>
+        <x:v>午餐
+¥50/人/天 × 8 人 × 7 天</x:v>
       </x:c>
       <x:c r="C40" s="34"/>
       <x:c r="D40" s="34"/>
       <x:c r="E40" s="47" t="n">
-        <x:v>20</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F40" s="32" t="n">
         <x:v>56</x:v>
       </x:c>
       <x:c r="G40" s="48" t="n">
         <x:f>ROUND(E40*F40,0)</x:f>
-        <x:v>1120</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="H40" s="48" t="n">
         <x:f>ROUND(G40/8,0)</x:f>
-        <x:v>140</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="I40" s="34" t="str">
-        <x:v>部分酒店含早，按全程保守预留</x:v>
+        <x:v>含 D6、D7 两次随车干粮，按西北公路餐饮规划值</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="58" customHeight="1">
@@ -2576,27 +2583,27 @@
         <x:v>餐饮</x:v>
       </x:c>
       <x:c r="B41" s="34" t="str">
-        <x:v>午餐
-¥50/人/天 × 8 人 × 7 天</x:v>
+        <x:v>晚餐
+¥70/人/天 × 8 人 × 7 天</x:v>
       </x:c>
       <x:c r="C41" s="34"/>
       <x:c r="D41" s="34"/>
       <x:c r="E41" s="47" t="n">
-        <x:v>50</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F41" s="32" t="n">
         <x:v>56</x:v>
       </x:c>
       <x:c r="G41" s="48" t="n">
         <x:f>ROUND(E41*F41,0)</x:f>
-        <x:v>2800</x:v>
+        <x:v>3920</x:v>
       </x:c>
       <x:c r="H41" s="48" t="n">
         <x:f>ROUND(G41/8,0)</x:f>
-        <x:v>350</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="I41" s="34" t="str">
-        <x:v>西北公路餐饮规划值</x:v>
+        <x:v>按西宁、茶卡、大柴旦、敦煌、张掖等地餐饮规划值</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="58" customHeight="1">
@@ -2604,55 +2611,55 @@
         <x:v>餐饮</x:v>
       </x:c>
       <x:c r="B42" s="34" t="str">
-        <x:v>晚餐
-¥70/人/天 × 8 人 × 7 天</x:v>
+        <x:v>饮水及零食
+¥20/人/天 × 8 人 × 7 天</x:v>
       </x:c>
       <x:c r="C42" s="34"/>
       <x:c r="D42" s="34"/>
       <x:c r="E42" s="47" t="n">
-        <x:v>70</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F42" s="32" t="n">
         <x:v>56</x:v>
       </x:c>
       <x:c r="G42" s="48" t="n">
         <x:f>ROUND(E42*F42,0)</x:f>
-        <x:v>3920</x:v>
+        <x:v>1120</x:v>
       </x:c>
       <x:c r="H42" s="48" t="n">
         <x:f>ROUND(G42/8,0)</x:f>
-        <x:v>490</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="I42" s="34" t="str">
-        <x:v>西北城市及景区周边餐饮规划值</x:v>
+        <x:v>长途驾驶补给预留</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="58" customHeight="1">
       <x:c r="A43" s="32" t="str">
-        <x:v>餐饮</x:v>
+        <x:v>物资及机动</x:v>
       </x:c>
       <x:c r="B43" s="34" t="str">
-        <x:v>饮水及零食
-¥20/人/天 × 8 人 × 7 天</x:v>
+        <x:v>氧气、常用药和应急用品
+¥200/人 × 8 人</x:v>
       </x:c>
       <x:c r="C43" s="34"/>
       <x:c r="D43" s="34"/>
       <x:c r="E43" s="47" t="n">
-        <x:v>20</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="F43" s="32" t="n">
-        <x:v>56</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="G43" s="48" t="n">
         <x:f>ROUND(E43*F43,0)</x:f>
-        <x:v>1120</x:v>
+        <x:v>1600</x:v>
       </x:c>
       <x:c r="H43" s="48" t="n">
         <x:f>ROUND(G43/8,0)</x:f>
-        <x:v>140</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="I43" s="34" t="str">
-        <x:v>长途驾驶补给预留</x:v>
+        <x:v>高原、荒漠和长途路段随车物资预留</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="58" customHeight="1">
@@ -2660,93 +2667,66 @@
         <x:v>物资及机动</x:v>
       </x:c>
       <x:c r="B44" s="34" t="str">
-        <x:v>氧气、常用药和应急用品
-¥200/人 × 8 人</x:v>
+        <x:v>机动金
+上述费用小计的约 5%</x:v>
       </x:c>
       <x:c r="C44" s="34"/>
       <x:c r="D44" s="34"/>
-      <x:c r="E44" s="47" t="n">
-        <x:v>200</x:v>
+      <x:c r="E44" s="50" t="n">
+        <x:v>0.05</x:v>
       </x:c>
       <x:c r="F44" s="32" t="n">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G44" s="48" t="n">
-        <x:f>ROUND(E44*F44,0)</x:f>
-        <x:v>1600</x:v>
+        <x:f>ROUND(SUM(G14:G43)*E44,0)</x:f>
+        <x:v>2182</x:v>
       </x:c>
       <x:c r="H44" s="48" t="n">
         <x:f>ROUND(G44/8,0)</x:f>
-        <x:v>200</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="I44" s="34" t="str">
-        <x:v>高原及荒漠路段随车物资预留</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" ht="58" customHeight="1">
-      <x:c r="A45" s="32" t="str">
-        <x:v>物资及机动</x:v>
-      </x:c>
-      <x:c r="B45" s="34" t="str">
-        <x:v>机动金
-上述费用小计的约 5%</x:v>
-      </x:c>
-      <x:c r="C45" s="34"/>
-      <x:c r="D45" s="34"/>
-      <x:c r="E45" s="50" t="n">
-        <x:v>0.05</x:v>
-      </x:c>
-      <x:c r="F45" s="32" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G45" s="48" t="n">
-        <x:f>ROUND(SUM(G14:G44)*E45,0)</x:f>
-        <x:v>2300</x:v>
-      </x:c>
-      <x:c r="H45" s="48" t="n">
+        <x:v>用于旺季价格波动、临时补给和小额改签</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="42" customHeight="1">
+      <x:c r="A45" s="38" t="str">
+        <x:v>费用合计</x:v>
+      </x:c>
+      <x:c r="B45" s="38" t="str">
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="C45" s="38"/>
+      <x:c r="D45" s="38"/>
+      <x:c r="E45" s="38"/>
+      <x:c r="F45" s="38"/>
+      <x:c r="G45" s="52" t="n">
+        <x:f>SUM(G14:G44)</x:f>
+        <x:v>45831</x:v>
+      </x:c>
+      <x:c r="H45" s="52" t="n">
         <x:f>ROUND(G45/8,0)</x:f>
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="I45" s="34" t="str">
-        <x:v>用于价格波动、临时补给和小额改签</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" ht="42" customHeight="1">
-      <x:c r="A46" s="38" t="str">
-        <x:v>费用合计</x:v>
-      </x:c>
-      <x:c r="B46" s="38" t="str">
-        <x:v>合计</x:v>
-      </x:c>
-      <x:c r="C46" s="38"/>
-      <x:c r="D46" s="38"/>
-      <x:c r="E46" s="38"/>
-      <x:c r="F46" s="38"/>
-      <x:c r="G46" s="52" t="n">
-        <x:f>SUM(G14:G45)</x:f>
-        <x:v>48301</x:v>
-      </x:c>
-      <x:c r="H46" s="52" t="n">
-        <x:f>ROUND(G46/8,0)</x:f>
-        <x:v>6038</x:v>
-      </x:c>
-      <x:c r="I46" s="38" t="str">
+        <x:v>5729</x:v>
+      </x:c>
+      <x:c r="I45" s="38" t="str">
         <x:v>按 8 人测算</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="64" customHeight="1">
-      <x:c r="A47" s="41" t="str">
-        <x:v>不含项目：不含往返西宁/敦煌的大交通、个人购物、单房差及未列明的自选娱乐项目。租车与异地还车费必须在下单前以平台结算页重新核验。 自选项目（未计入）：鸣沙山骑骆驼、滑沙、越野车等自选项目、莫高窟特窟票、茶卡盐湖游船、观光塔等自选项目。</x:v>
-      </x:c>
-      <x:c r="B47" s="41"/>
-      <x:c r="C47" s="41"/>
-      <x:c r="D47" s="41"/>
-      <x:c r="E47" s="41"/>
-      <x:c r="F47" s="41"/>
-      <x:c r="G47" s="41"/>
-      <x:c r="H47" s="41"/>
-      <x:c r="I47" s="41"/>
-    </x:row>
+    <x:row r="46" ht="64" customHeight="1">
+      <x:c r="A46" s="41" t="str">
+        <x:v>不含项目：不含抵达西宁和离开西宁的大交通、个人购物、单房差及未列明的自选娱乐项目。租车与酒店价格须在下单前以平台结算页重新核验。 自选项目（未计入）：鸣沙山骑骆驼、滑沙、越野车等自选项目、莫高窟特窟票、茶卡盐湖游船、观光塔等自选项目、青海湖临时进入收费景区的门票。</x:v>
+      </x:c>
+      <x:c r="B46" s="41"/>
+      <x:c r="C46" s="41"/>
+      <x:c r="D46" s="41"/>
+      <x:c r="E46" s="41"/>
+      <x:c r="F46" s="41"/>
+      <x:c r="G46" s="41"/>
+      <x:c r="H46" s="41"/>
+      <x:c r="I46" s="41"/>
+    </x:row>
+    <x:row r="47" ht="2" customHeight="1"/>
     <x:row r="48" ht="2" customHeight="1"/>
     <x:row r="49" ht="2" customHeight="1"/>
     <x:row r="50" ht="2" customHeight="1"/>
@@ -2800,8 +2780,7 @@
     <x:mergeCell ref="B43:D43"/>
     <x:mergeCell ref="B44:D44"/>
     <x:mergeCell ref="B45:D45"/>
-    <x:mergeCell ref="B46:D46"/>
-    <x:mergeCell ref="A47:I47"/>
+    <x:mergeCell ref="A46:I46"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
